--- a/Result/checksun_type/化妝品.xlsx
+++ b/Result/checksun_type/化妝品.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>16.6</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>16.74</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>16.97</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>16.74</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>16.97</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>4837481.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>4898844.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>4898844.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>6522159.0</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>7467257.5</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>7467257.5</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-510468.3037822163</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>4837481</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>4837481.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>16.47</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>16.74</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>16.97</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>16.74</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>16.97</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>1318745.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>6868173.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>6868173.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>6493460.2</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>7528953.3</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>7528953.3</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-486853.7959417813</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>1318745</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>1318745.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>16.46</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>16.76</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>16.98</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>16.76</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>16.98</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>6158586.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>7942264.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>7942264</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>6735639.1</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>7598178.06</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>7598178.06</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-58723.72060038242</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>6158586</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>6158586.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>16.49</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>16.78</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>16.99</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>16.99</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>7947232.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>7489543.2</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>7489543.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>6958233.1</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>7762346.68</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>7762346.68</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>36433.55562305823</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>7947232</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>7947232.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>16.63</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>16.85</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>17.0</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>16.85</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>17</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>4232178.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>8620782.8</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>8620782.800000001</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>6890359.7</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>7694953.34</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>7694953.34</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-20569.31961570866</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>4232178</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>4232178.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>16.72</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>16.91</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>17.02</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>16.91</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>17.02</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>14684125.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>8145473.6</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>8145473.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>6803172.5</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>7656264.52</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>7656264.52</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>296774.1200294727</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>14684125</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>14684125.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>16.83</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>16.95</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>17.03</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>16.95</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>17.03</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>6689199.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>6118747.2</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>6118747.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>5574574.1</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>7444881.34</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>7444881.34</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-380328.6490498912</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>6689199</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>6689199.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>16.81</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>16.97</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>17.04</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>16.97</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>17.04</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>3894982.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>5529014.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>5529014.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>5491244.3</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>7354839.54</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>7354839.54</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-477435.9388400586</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>3894982</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>3894982.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>16.76</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>16.98</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>17.03</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>17.03</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>13603430.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>6426923.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>6426923</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>5411234.1</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>7385529.72</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>7385529.72</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-299728.9621531535</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>13603430</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>13603430.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>16.7</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>16.98</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>17.03</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>17.03</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>1855632.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>5159936.6</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>5159936.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>4534923.5</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>7286760.8</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>7286760.8</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-1075348.103952104</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>1855632</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>1855632.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>16.72</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>16.98</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>17.03</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>17.03</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>4550493.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>5460871.4</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>5460871.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>4599369.5</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>7406016.88</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>7406016.88</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-886277.5170951728</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>4550493</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>4550493.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>43.2</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>43.2</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>45.12</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>45.12</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>3383849.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>2709230.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>2709230</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>2380673.2</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>5209044.42</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>5209044.42</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-29116.58208910562</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>3383849</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>3383849.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>42.84</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>43.3</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>45.22</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>45.22</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>3775435.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>2142386.0</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>2142386</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>2385309.8</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>5210679.64</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>5210679.64</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-103339.04511018</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>3775435</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>3775435.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>42.52999999999999</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>43.45</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>45.36</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>43.45</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>45.36</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>3711041.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>1585357.8</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>1585357.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>2538671.3</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>5178587.7</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>5178587.7</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-247636.0978149222</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>3711041</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>3711041.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>42.4</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>43.63</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>45.49</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>43.63</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>45.49</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>937215.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>1363163.2</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>1363163.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>2470234.2</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>5145449.24</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>5145449.24</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-438031.241042593</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>937215</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>937215.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>42.77</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>43.86</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>45.64</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>43.86</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>45.64</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>1738610.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>2232151.8</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>2232151.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>2531162.0</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>5179004.82</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>5179004.82</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-397184.6870448873</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>1738610</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>1738610.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>42.82</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>44.02</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>45.8</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>44.02</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>45.8</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>549629.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>2052116.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>2052116.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>2595180.8</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>5266456.46</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>5266456.46</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-410511.0496537043</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>549629</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>549629.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>43.13</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>44.15</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>45.95</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>44.15</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>45.95</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>990294.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>2628233.6</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>2628233.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>2769274.0</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>5285586.92</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>5285586.92</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-287496.7801786675</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>990294</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>990294.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>43.39</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>46.11</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>46.11</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>2600068.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>3491984.8</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>3491984.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>2750464.3</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>5284330.0</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>5284330</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-148708.4744936624</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>2600068</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>2600068.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>43.36</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>44.48</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>46.25</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>44.48</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>46.25</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>5282158.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>3577305.2</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>3577305.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>2611522.3</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>5283426.94</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>5283426.94</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-117604.2351403106</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>5282158</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>5282158.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>42.98</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>44.61</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>46.35</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>44.61</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>46.35</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>838433.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>2830172.2</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>2830172.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>2518129.9</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>5219863.88</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>5219863.88</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-356336.2419519396</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>838433</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>838433.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>42.95</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>44.81</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>46.5</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>44.81</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>46.5</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>3430215.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>3138245.2</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>3138245.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>2526129.4</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>5240025.44</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>5240025.44</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-208542.2787559833</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>3430215</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>3430215.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>65.5</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>65.36</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>67.28</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>65.36</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>67.28</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>6593415.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>6870811.6</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>6870811.6</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>7539266.8</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>8370856.4</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>8370856.4</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-337320.8808771009</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>6593415</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>6593415.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>65.1</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>65.29</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>67.36</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>65.29000000000001</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>67.36</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>3304924.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>6532469.4</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>6532469.4</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>8902004.9</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>8485961.74</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>8485961.74</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-334975.1041183937</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>3304924</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>3304924.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>64.82000000000001</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>65.28</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>67.49</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>65.28</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>67.48999999999999</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>9381048.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>7185743.2</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>7185743.2</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>8845438.6</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>8642112.38</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>8642112.380000001</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>32677.72354113031</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>9381048</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>9381048.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>64.94</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>65.35</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>67.62</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>65.34999999999999</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>67.62</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>8570631.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>6723071.4</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>6723071.4</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>8714002.9</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>8623529.2</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>8623529.199999999</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-94284.29850030411</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>8570631</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>8570631.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>65.76</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>65.55</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>65.55</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>67.8</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>6504040.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>8142815.0</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>8142815</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>8334073.6</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>8675810.86</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>8675810.859999999</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-185460.9264701987</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>6504040</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>6504040.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>66.0</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>65.72</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>67.97</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>65.72</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>67.97</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>4901704.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>8207722.0</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>8207722</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>8228897.2</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>8714393.32</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>8714393.32</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-87669.18333896995</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>4901704</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>4901704.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>66.36</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>65.79</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>68.13</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>65.79000000000001</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>68.13</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>6571293.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>11271540.4</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>11271540.4</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>8635132.0</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>8837532.54</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>8837532.539999999</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>226843.2062534634</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>6571293</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>6571293.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>66.06</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>65.82</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>68.27</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>65.81999999999999</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>68.27</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>7067689.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>10505134.0</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>10505134</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>8625852.6</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>9442530.94</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>9442530.939999999</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>489160.5411621742</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>7067689</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>7067689.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>65.38</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>65.83</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>68.36</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>65.83</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>68.36</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>15669349.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>10704934.4</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>10704934.4</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>8234938.5</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>9546296.88</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>9546296.880000001</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>793244.2859902531</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>15669349</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>15669349.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>64.62</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>65.74</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>68.4</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>65.73999999999999</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>68.40000000000001</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>6828575.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>8525332.2</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>8525332.199999999</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>7126370.3</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>9341481.26</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>9341481.26</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>277713.0541021423</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>6828575</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>6828575.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>64.34</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>68.49</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>68.48999999999999</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>20220796.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>8250072.4</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>8250072.4</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>7064739.2</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>9422715.92</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>9422715.92</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>478547.3280440522</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>20220796</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>20220796.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>31.77999999999999</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>31.79</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>31.97</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>31.79</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>31.97</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>24752845.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>6361239.8</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>6361239.8</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>5173323.2</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>3811369.74</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>3811369.74</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>1376921.324417498</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>24752845</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>24752845.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>31.72</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>31.79</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>31.97</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>31.79</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>31.97</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>661190.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>1925877.6</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>1925877.6</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>3004447.9</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>3413913.34</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>3413913.34</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-340719.2026818991</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>661190</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>661190.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>31.69</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>31.8</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>31.98</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>31.98</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>2415396.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>2458628.0</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>2458628</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>3310550.9</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>3561770.12</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>3561770.12</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-201074.0912995418</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>2415396</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>2415396.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>31.66</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>31.8</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>31.99</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>31.99</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>2208385.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>2853136.2</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>2853136.2</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>3195480.8</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>3578602.06</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>3578602.06</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-182350.5003497619</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>2208385</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>2208385.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>31.65</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>31.82</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>32.0</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>31.82</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>32</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>1768383.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>3478744.6</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>3478744.6</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>3297831.0</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>3557480.34</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>3557480.34</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-126910.2454090137</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>1768383</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>1768383.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>31.69</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>31.83</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>32.01</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>31.83</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>32.01</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>2576034.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>3985406.6</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>3985406.6</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>3305598.3</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>3562799.06</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>3562799.06</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>3965.698985234834</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>2576034</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>2576034.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>31.74</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>31.85</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>32.03</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>31.85</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>32.03</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>3324942.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>4083018.2</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>4083018.2</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>3290697.3</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>3542785.62</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>3542785.62</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>104255.6660132594</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>3324942</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>3324942.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>31.78</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>31.87</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>32.04</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>31.87</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>32.04</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>4387937.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>4162473.8</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>4162473.8</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>3284508.8</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>3530449.16</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>3530449.16</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>163563.487981393</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>4387937</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>4387937.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>31.78</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>31.88</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>32.05</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>31.88</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>32.05</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>5336427.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>3537825.4</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>3537825.4</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>3443786.9</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>3484907.42</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>3484907.42</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>128555.0733651058</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>5336427</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>5336427.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>31.81</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>31.89</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>32.06</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>31.89</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>32.06</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>4301693.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>3116917.4</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>3116917.4</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>3381785.1</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>3490553.5</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>3490553.5</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-27672.12870691577</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>4301693</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>4301693.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>31.8</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>31.9</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>32.06</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>32.06</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>3064092.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>2625790.0</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>2625790</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>3337253.8</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>3465493.34</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>3465493.34</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-139001.1984988428</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>3064092</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>3064092.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>

--- a/Result/checksun_type/化妝品.xlsx
+++ b/Result/checksun_type/化妝品.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CX23"/>
+  <dimension ref="A1:CX25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -953,12 +953,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-5.65</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2904.755</t>
+          <t>4190.357</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -983,12 +983,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>87.56</t>
+          <t>87.93</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1128,17 +1128,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>12.70</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1149,50 +1149,50 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>2905</t>
+          <t>4190</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>37.14</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>59.05</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>-4.33</v>
+        <v>-3.06</v>
       </c>
       <c r="AV2" t="n">
-        <v>5.93</v>
+        <v>6.94</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>17.77</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>16.77</v>
+        <v>16.83</v>
       </c>
       <c r="BA2" t="n">
-        <v>16.72</v>
+        <v>16.74</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
@@ -1201,14 +1201,14 @@
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>142.98</t>
+          <t>89.01</t>
         </is>
       </c>
       <c r="BD2" t="n">
         <v>0.28</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-86.85</t>
+          <t>-83.08</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1227,43 +1227,43 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>42060788.49130435</t>
+          <t>69092285.6590909</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>50050807.0</t>
+          <t>74227869.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>95018011.2</v>
+        <v>107145825</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>50659715.5</t>
+          <t>57014855.3</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>13784987.5</v>
+        <v>15184901.32</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>44358295</t>
+          <t>50130969</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>7972830.290890622</t>
+          <t>9493853.109026255</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>20307128.75871883</t>
+          <t>17859478.60877223</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>50050807.0</t>
+          <t>74227869.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1338,12 +1338,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>34.62</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>3321</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1393,22 +1393,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -1445,12 +1445,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-7.69</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>14269.838</t>
+          <t>2904.755</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1470,17 +1470,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>85.38</t>
+          <t>87.56</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1620,17 +1620,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>43.24</t>
+          <t>8.80</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-17.76</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1641,50 +1641,50 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>2905</t>
+          <t>4190</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>52.86</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>84.29</t>
+          <t>59.05</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>2.27</v>
+        <v>-4.33</v>
       </c>
       <c r="AV3" t="n">
-        <v>5.04</v>
+        <v>5.93</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.77</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>16.76</v>
+        <v>16.77</v>
       </c>
       <c r="BA3" t="n">
-        <v>16.7</v>
+        <v>16.72</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
@@ -1693,14 +1693,14 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>334.39</t>
+          <t>142.98</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>0.32</v>
+        <v>0.28</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-91.55</t>
+          <t>-86.85</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1719,43 +1719,43 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>42060788.49130435</t>
+          <t>69092285.6590909</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>271794825.0</t>
+          <t>50050807.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>85900227.8</v>
+        <v>95018011.2</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>46337047.2</t>
+          <t>50659715.5</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>13077653.86</v>
+        <v>13784987.5</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>39563180</t>
+          <t>44358295</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>5730230.569467312</t>
+          <t>7972830.290890622</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>25668916.73154542</t>
+          <t>20307128.75871883</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>271794825.0</t>
+          <t>50050807.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1820,22 +1820,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1860,12 +1860,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>34.62</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>3321</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1885,22 +1885,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -1937,12 +1937,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>8.91</t>
+          <t>-7.69</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4345.538</t>
+          <t>14269.838</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1962,17 +1962,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-15.59</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>66.07</t>
+          <t>85.38</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2112,87 +2112,87 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>13.17</t>
+          <t>43.24</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-17.76</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>2905</t>
+          <t>4190</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>52.86</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>84.29</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>13.98</v>
+        <v>2.27</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.39</v>
+        <v>5.04</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>16.68</v>
+        <v>16.76</v>
       </c>
       <c r="BA4" t="n">
-        <v>16.68</v>
+        <v>16.7</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>2107.80</t>
+          <t>334.39</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>0.27</v>
+        <v>0.32</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-98.61</t>
+          <t>-91.55</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2211,43 +2211,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>42060788.49130435</t>
+          <t>69092285.6590909</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>85383179.0</t>
+          <t>271794825.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>32469406.2</v>
+        <v>85900227.8</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>19551967.8</t>
+          <t>46337047.2</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>7775541.34</v>
+        <v>13077653.86</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>12917438</t>
+          <t>39563180</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>2105014.903634928</t>
+          <t>5730230.569467312</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>8653579.166599646</t>
+          <t>25668916.73154542</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>85383179.0</t>
+          <t>271794825.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>9.17</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2312,22 +2312,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>34.62</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>3321</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2377,22 +2377,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2412,14 +2412,14 @@
       </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2429,12 +2429,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>8.91</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3052.112</t>
+          <t>4345.538</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2454,17 +2454,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-12.61</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>43.47</t>
+          <t>66.07</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2604,17 +2604,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>9.25</t>
+          <t>13.17</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2625,12 +2625,12 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>2905</t>
+          <t>4190</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2640,51 +2640,51 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>8.029999999999999</v>
+        <v>13.98</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.3</v>
+        <v>3.39</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>16.57</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>16.52</v>
+        <v>16.68</v>
       </c>
       <c r="BA5" t="n">
-        <v>16.62</v>
+        <v>16.68</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>153.51</t>
+          <t>2107.80</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>0.03</v>
+        <v>0.27</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-105.92</t>
+          <t>-98.61</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2703,43 +2703,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>42060788.49130435</t>
+          <t>69092285.6590909</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>54272445.0</t>
+          <t>85383179.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>16472858.2</v>
+        <v>32469406.2</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>11482077.0</t>
+          <t>19551967.8</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>6145777.4</v>
+        <v>7775541.34</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>4990781</t>
+          <t>12917438</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>914366.8558231613</t>
+          <t>2105014.903634928</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>4009574.032155704</t>
+          <t>8653579.166599646</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>54272445.0</t>
+          <t>85383179.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>9.17</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>34.62</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>3321</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2869,22 +2869,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2904,14 +2904,14 @@
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>827.557</t>
+          <t>3052.112</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2946,17 +2946,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>43.47</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3096,17 +3096,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>9.25</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>5.60</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3117,66 +3117,66 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>2905</t>
+          <t>4190</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>0.37</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="AV6" t="n">
-        <v>-1.31</v>
+        <v>0.3</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>16.24</t>
+          <t>16.57</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>16.45</v>
+        <v>16.52</v>
       </c>
       <c r="BA6" t="n">
-        <v>16.6</v>
+        <v>16.62</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>16.77</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-40.86</t>
+          <t>153.51</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>-0.1</v>
+        <v>0.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.05</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-108.19</t>
+          <t>-105.92</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3195,43 +3195,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>42060788.49130435</t>
+          <t>69092285.6590909</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>13588800.0</t>
+          <t>54272445.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>6883885.6</v>
+        <v>16472858.2</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>6630741.6</t>
+          <t>11482077.0</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>5332397.1</v>
+        <v>6145777.4</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>253144</t>
+          <t>4990781</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>351601.9146717899</t>
+          <t>914366.8558231613</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>565374.8389445115</t>
+          <t>4009574.032155704</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>13588800.0</t>
+          <t>54272445.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>-9.44</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3296,22 +3296,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>34.62</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>3321</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3361,22 +3361,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -3413,12 +3413,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>275.868</t>
+          <t>827.557</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>16.15</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3438,17 +3438,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3588,17 +3588,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3609,66 +3609,66 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>2905</t>
+          <t>4190</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-0.68</v>
+        <v>0.37</v>
       </c>
       <c r="AV7" t="n">
-        <v>-1.26</v>
+        <v>-1.31</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>16.24</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>16.47</v>
+        <v>16.45</v>
       </c>
       <c r="BA7" t="n">
-        <v>16.61</v>
+        <v>16.6</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>16.77</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-56.60</t>
+          <t>-40.86</t>
         </is>
       </c>
       <c r="BD7" t="n">
         <v>-0.1</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-107.35</t>
+          <t>-108.19</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3687,43 +3687,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>42060788.49130435</t>
+          <t>69092285.6590909</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>4461890.0</t>
+          <t>13588800.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>6301419.8</v>
+        <v>6883885.6</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>6577320.7</t>
+          <t>6630741.6</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>5097733.74</v>
+        <v>5332397.1</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-275900</t>
+          <t>253144</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>312734.1102585678</t>
+          <t>351601.9146717899</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-16139.71703378018</t>
+          <t>565374.8389445115</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>4461890.0</t>
+          <t>13588800.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>-10.28</t>
+          <t>-9.44</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>34.62</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>3321</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3858,17 +3858,17 @@
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>16.35</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>16.15</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>16.15</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="CX7" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -3905,12 +3905,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>285.969</t>
+          <t>275.868</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>16.15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3930,17 +3930,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>7.45</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -4080,17 +4080,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4101,12 +4101,12 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>2905</t>
+          <t>4190</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -4120,44 +4120,44 @@
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-0.92</v>
+        <v>-0.68</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0.85</v>
+        <v>-1.26</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>16.35</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>16.49</v>
+        <v>16.47</v>
       </c>
       <c r="BA8" t="n">
-        <v>16.62</v>
+        <v>16.61</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-51.70</t>
+          <t>-56.60</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>-0.08</v>
+        <v>-0.1</v>
       </c>
       <c r="BE8" t="n">
         <v>-0.06</v>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-106.31</t>
+          <t>-107.35</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4179,43 +4179,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>42060788.49130435</t>
+          <t>69092285.6590909</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>4640717.0</t>
+          <t>4461890.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>6773866.6</v>
+        <v>6301419.8</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>6953049.8</t>
+          <t>6577320.7</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>5099505.8</v>
+        <v>5097733.74</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-179183</t>
+          <t>-275900</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>372529.3515844492</t>
+          <t>312734.1102585678</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>131584.8357484369</t>
+          <t>-16139.71703378018</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>4640717.0</t>
+          <t>4461890.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>-10.00</t>
+          <t>-10.28</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>34.62</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>3321</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4345,14 +4345,14 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
           <t>16.35</t>
         </is>
       </c>
-      <c r="CR8" t="inlineStr">
-        <is>
-          <t>16.35</t>
-        </is>
-      </c>
       <c r="CS8" t="inlineStr">
         <is>
           <t>16.15</t>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>16.15</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="CX8" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>332.074</t>
+          <t>285.969</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4422,17 +4422,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4572,17 +4572,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4593,66 +4593,66 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>2905</t>
+          <t>4190</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="AU9" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="AV9" t="n">
         <v>-0.85</v>
       </c>
-      <c r="AV9" t="n">
-        <v>-0.47</v>
-      </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>16.44</t>
+          <t>16.35</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>16.52</v>
+        <v>16.49</v>
       </c>
       <c r="BA9" t="n">
-        <v>16.63</v>
+        <v>16.62</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-37.24</t>
+          <t>-51.70</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="BE9" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-105.50</t>
+          <t>-106.31</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4671,43 +4671,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>42060788.49130435</t>
+          <t>69092285.6590909</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>5400439.0</t>
+          <t>4640717.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>6634529.4</v>
+        <v>6773866.6</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>6936334.7</t>
+          <t>6953049.8</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>5081502.14</v>
+        <v>5099505.8</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-301805</t>
+          <t>-179183</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>416337.4453728151</t>
+          <t>372529.3515844492</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>318760.4170177318</t>
+          <t>131584.8357484369</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>5400439.0</t>
+          <t>4640717.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>-9.44</t>
+          <t>-10.00</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>34.62</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>3321</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>16.35</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
@@ -4847,14 +4847,14 @@
       </c>
       <c r="CS9" t="inlineStr">
         <is>
+          <t>16.15</t>
+        </is>
+      </c>
+      <c r="CT9" t="inlineStr">
+        <is>
           <t>16.2</t>
         </is>
       </c>
-      <c r="CT9" t="inlineStr">
-        <is>
-          <t>16.3</t>
-        </is>
-      </c>
       <c r="CU9" t="inlineStr">
         <is>
           <t>11.58</t>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="CX9" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -4889,12 +4889,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>388.233</t>
+          <t>332.074</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4904,149 +4904,149 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>16.3</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>6.59</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-4.35</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025/10/17</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17.1</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>16.95</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>17.8</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>2026/01/20</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
           <t>16.25</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>4.41</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-0.69</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>-9.80</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2025/10/17</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>17.1</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2025/11/06</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>16.95</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>2025/07/07</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>17.8</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>2026/01/20</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>16.25</t>
-        </is>
-      </c>
       <c r="AI10" t="inlineStr">
         <is>
           <t>2025/12/26</t>
@@ -5064,17 +5064,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5085,67 +5085,67 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>2905</t>
+          <t>4190</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>-1.69</v>
+        <v>-0.85</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0.06</v>
+        <v>-0.47</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>16.53</t>
+          <t>16.44</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>16.54</v>
+        <v>16.52</v>
       </c>
       <c r="BA10" t="n">
-        <v>16.64</v>
+        <v>16.63</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-20.44</t>
+          <t>-37.24</t>
         </is>
       </c>
       <c r="BD10" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="BE10" t="n">
         <v>-0.05</v>
       </c>
-      <c r="BE10" t="n">
-        <v>-0.04</v>
-      </c>
       <c r="BF10" t="inlineStr">
         <is>
           <t>0.87</t>
@@ -5153,7 +5153,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-104.99</t>
+          <t>-105.50</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5163,43 +5163,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>42060788.49130435</t>
+          <t>69092285.6590909</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>6327582.0</t>
+          <t>5400439.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>6491295.8</v>
+        <v>6634529.4</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>7196752.8</t>
+          <t>6936334.7</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>5141183.88</v>
+        <v>5081502.14</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-705457</t>
+          <t>-301805</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>434078.7232555575</t>
+          <t>416337.4453728151</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>493371.0182232345</t>
+          <t>318760.4170177318</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>6327582.0</t>
+          <t>5400439.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>-9.72</t>
+          <t>-9.44</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>34.62</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>3321</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5329,22 +5329,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>16.25</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>16.35</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>16.25</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>16.25</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5364,14 +5364,14 @@
       </c>
       <c r="CX10" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5381,12 +5381,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>648.754</t>
+          <t>388.233</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>16.25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5406,17 +5406,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-10.37</t>
+          <t>-9.80</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5556,17 +5556,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5577,63 +5577,63 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>2905</t>
+          <t>4190</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>50.93</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>-1.32</v>
+        <v>-1.69</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.36</v>
+        <v>-0.06</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>16.62</t>
+          <t>16.53</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>16.56</v>
+        <v>16.54</v>
       </c>
       <c r="BA11" t="n">
-        <v>16.65</v>
+        <v>16.64</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>16.83</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>28.78</t>
+          <t>-20.44</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>-0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="BE11" t="n">
         <v>-0.04</v>
@@ -5645,7 +5645,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-104.73</t>
+          <t>-104.99</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5655,43 +5655,43 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>42060788.49130435</t>
+          <t>69092285.6590909</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>10676471.0</t>
+          <t>6327582.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>6377597.6</v>
+        <v>6491295.8</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>7115866.6</t>
+          <t>7196752.8</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>5160002.2</v>
+        <v>5141183.88</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-738269</t>
+          <t>-705457</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>423298.3059887072</t>
+          <t>434078.7232555575</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>625857.5907231215</t>
+          <t>493371.0182232345</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>10676471.0</t>
+          <t>6327582.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>-8.89</t>
+          <t>-9.72</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>34.62</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>3321</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5821,22 +5821,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.25</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>16.35</t>
+          <t>16.25</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>16.25</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="CX11" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -5873,12 +5873,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>410.356</t>
+          <t>648.754</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5898,17 +5898,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>-10.37</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -6048,17 +6048,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6069,63 +6069,63 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>2905</t>
+          <t>4190</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>50.93</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>-0.6</v>
+        <v>-1.32</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.77</v>
+        <v>0.36</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>16.62</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>16.57</v>
+        <v>16.56</v>
       </c>
       <c r="BA12" t="n">
-        <v>16.66</v>
+        <v>16.65</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>16.84</t>
+          <t>16.83</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>66.43</t>
+          <t>28.78</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="BE12" t="n">
         <v>-0.04</v>
@@ -6137,7 +6137,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-105.07</t>
+          <t>-104.73</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6147,43 +6147,43 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>42060788.49130435</t>
+          <t>69092285.6590909</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>6824124.0</t>
+          <t>10676471.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>6853221.6</v>
+        <v>6377597.6</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>6771786.2</t>
+          <t>7115866.6</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>5013678.9</v>
+        <v>5160002.2</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>81435</t>
+          <t>-738269</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>386469.3451279046</t>
+          <t>423298.3059887072</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>326819.6731971363</t>
+          <t>625857.5907231215</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>6824124.0</t>
+          <t>10676471.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>-7.78</t>
+          <t>-8.89</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -6288,12 +6288,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>34.62</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>3321</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6313,22 +6313,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>16.35</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="CX12" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -6365,12 +6365,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>197.457</t>
+          <t>226.35</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>82.98</t>
+          <t>85.50</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6410,37 +6410,37 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-06-27 00:00:00</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-07 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-07 00:00:00</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-13 00:00:00</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -6450,12 +6450,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -6465,22 +6465,22 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-30.23</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024/11/05</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -6490,7 +6490,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6540,17 +6540,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>13.23</t>
+          <t>15.16</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6566,61 +6566,61 @@
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>19.41</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>54.31</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>-4.37</v>
+        <v>-4.81</v>
       </c>
       <c r="AV13" t="n">
-        <v>4.72</v>
+        <v>5.5</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>44.13</t>
+          <t>44.49</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>42.14</v>
+        <v>42.17</v>
       </c>
       <c r="BA13" t="n">
-        <v>42.4</v>
+        <v>42.39</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>43.26</t>
+          <t>43.22</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>453.26</t>
+          <t>167.39</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>0.46</v>
+        <v>0.38</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
@@ -6629,7 +6629,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-91.42</t>
+          <t>-85.25</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6639,43 +6639,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>6791742.917391304</t>
+          <t>7435306.067193676</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>8413534.0</t>
+          <t>9926503.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>29380362.6</v>
+        <v>30954151</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>16056599.7</t>
+          <t>16686600.8</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>4904141.1</v>
+        <v>5067898.96</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>13323762</t>
+          <t>14267550</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>2548920.429110818</t>
+          <t>2727067.001083214</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>5189350.169846542</t>
+          <t>3706873.146931395</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>8413534.0</t>
+          <t>9926503.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>-28.84</t>
+          <t>-28.58</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6780,12 +6780,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>34.62</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>3064</t>
+          <t>3075</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6805,22 +6805,22 @@
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
-          <t>44.15</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>44.15</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="CX13" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -6857,12 +6857,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1195.571</t>
+          <t>197.457</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6882,17 +6882,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-4.86</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>81.41</t>
+          <t>82.98</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6902,37 +6902,37 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-06-27 00:00:00</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-07 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-07 00:00:00</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-13 00:00:00</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -6957,22 +6957,22 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-30.48</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024/11/05</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -7032,17 +7032,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>80.08</t>
+          <t>13.23</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>-19.10</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -7058,61 +7058,61 @@
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>43.53</t>
+          <t>19.41</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>81.18</t>
+          <t>54.31</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>1</v>
+        <v>-4.37</v>
       </c>
       <c r="AV14" t="n">
-        <v>4.09</v>
+        <v>4.72</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>43.81</t>
+          <t>44.13</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>42.09</v>
+        <v>42.14</v>
       </c>
       <c r="BA14" t="n">
         <v>42.4</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>43.29</t>
+          <t>43.26</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>5229.05</t>
+          <t>453.26</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>0.57</v>
+        <v>0.46</v>
       </c>
       <c r="BE14" t="n">
-        <v>-0.01</v>
+        <v>0.08</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-101.14</t>
+          <t>-91.42</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7131,43 +7131,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>6791742.917391304</t>
+          <t>7435306.067193676</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>56593114.0</t>
+          <t>8413534.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>28121272.4</v>
+        <v>29380362.6</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>15501784.3</t>
+          <t>16056599.7</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>4746863</v>
+        <v>4904141.1</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>12619488</t>
+          <t>13323762</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>2068842.294431595</t>
+          <t>2548920.429110818</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>7283944.37508795</t>
+          <t>5189350.169846542</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>56593114.0</t>
+          <t>8413534.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>-25.38</t>
+          <t>-28.84</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7232,22 +7232,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>34.62</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>3064</t>
+          <t>3075</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7297,22 +7297,22 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>44.15</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>44.15</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>44.15</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7332,7 +7332,7 @@
       </c>
       <c r="CX14" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -7349,12 +7349,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>924.579</t>
+          <t>1195.571</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7374,17 +7374,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-16.23</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>81.41</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7394,37 +7394,37 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-06-27 00:00:00</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-07 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-07 00:00:00</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-13 00:00:00</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -7434,12 +7434,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -7449,22 +7449,22 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-27.10</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024/11/05</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7524,17 +7524,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>61.93</t>
+          <t>80.08</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>-19.10</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7550,61 +7550,61 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>43.53</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>81.18</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>13.81</v>
+        <v>1</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.74</v>
+        <v>4.09</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.81</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>41.95</v>
+        <v>42.09</v>
       </c>
       <c r="BA15" t="n">
-        <v>42.35</v>
+        <v>42.4</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>43.31</t>
+          <t>43.29</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>413.12</t>
+          <t>5229.05</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>0.49</v>
+        <v>0.57</v>
       </c>
       <c r="BE15" t="n">
-        <v>-0.16</v>
+        <v>-0.01</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-116.07</t>
+          <t>-101.14</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7623,43 +7623,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>6791742.917391304</t>
+          <t>7435306.067193676</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>44888583.0</t>
+          <t>56593114.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>17133672.6</v>
+        <v>28121272.4</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>10065617.0</t>
+          <t>15501784.3</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>3634806.6</v>
+        <v>4746863</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>7068055</t>
+          <t>12619488</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>1120641.91613044</t>
+          <t>2068842.294431595</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>4853983.083465392</t>
+          <t>7283944.37508795</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>44888583.0</t>
+          <t>56593114.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>-17.28</t>
+          <t>-25.38</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7724,22 +7724,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>34.62</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>3064</t>
+          <t>3075</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7789,22 +7789,22 @@
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>44.15</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7824,14 +7824,14 @@
       </c>
       <c r="CX15" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>789.819</t>
+          <t>924.579</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7866,17 +7866,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-15.82</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>58.46</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7886,37 +7886,37 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-06-27 00:00:00</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-07 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-07 00:00:00</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-13 00:00:00</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -7926,12 +7926,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -7941,22 +7941,22 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-19.19</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024/11/05</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -8016,17 +8016,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>52.90</t>
+          <t>61.93</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>7.21</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -8052,51 +8052,51 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>7.55</v>
+        <v>13.81</v>
       </c>
       <c r="AV16" t="n">
-        <v>-0.22</v>
+        <v>2.74</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>41.47000000000001</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>41.56</v>
+        <v>41.95</v>
       </c>
       <c r="BA16" t="n">
-        <v>42.22</v>
+        <v>42.35</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.31</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>64.79</t>
+          <t>413.12</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>-0.11</v>
+        <v>0.49</v>
       </c>
       <c r="BE16" t="n">
-        <v>-0.32</v>
+        <v>-0.16</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-132.66</t>
+          <t>-116.07</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8115,43 +8115,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>6791742.917391304</t>
+          <t>7435306.067193676</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>34949021.0</t>
+          <t>44888583.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>9100308.4</v>
+        <v>17133672.6</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>5742805.4</t>
+          <t>10065617.0</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>2789036.3</v>
+        <v>3634806.6</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>3357503</t>
+          <t>7068055</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>441852.6129786303</t>
+          <t>1120641.91613044</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>2463310.16388083</t>
+          <t>4853983.083465392</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>34949021.0</t>
+          <t>44888583.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8171,7 +8171,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>-24.79</t>
+          <t>-17.28</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>34.62</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>3064</t>
+          <t>3075</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8281,22 +8281,22 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8316,14 +8316,14 @@
       </c>
       <c r="CX16" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -8333,12 +8333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>50.507</t>
+          <t>789.819</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8358,17 +8358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>58.46</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8378,37 +8378,37 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-06-27 00:00:00</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-07 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-07 00:00:00</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-13 00:00:00</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -8433,22 +8433,22 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-26.52</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024/11/05</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8508,17 +8508,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>52.90</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>7.21</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8534,42 +8534,42 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>-0.61</v>
+        <v>7.55</v>
       </c>
       <c r="AV17" t="n">
-        <v>-1.42</v>
+        <v>-0.22</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>41.47000000000001</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>41.39</v>
+        <v>41.56</v>
       </c>
       <c r="BA17" t="n">
         <v>42.22</v>
@@ -8581,14 +8581,14 @@
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-14.25</t>
+          <t>64.79</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>-0.42</v>
+        <v>-0.11</v>
       </c>
       <c r="BE17" t="n">
-        <v>-0.37</v>
+        <v>-0.32</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-137.95</t>
+          <t>-132.66</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8607,43 +8607,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>6791742.917391304</t>
+          <t>7435306.067193676</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>2057561.0</t>
+          <t>34949021.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>2419050.6</v>
+        <v>9100308.4</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>2423375.9</t>
+          <t>5742805.4</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>2195699.04</v>
+        <v>2789036.3</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-4325</t>
+          <t>3357503</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>74314.87645095764</t>
+          <t>441852.6129786303</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>25040.84433571342</t>
+          <t>2463310.16388083</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>2057561.0</t>
+          <t>34949021.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8663,7 +8663,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>-31.62</t>
+          <t>-24.79</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8708,22 +8708,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>34.62</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>3064</t>
+          <t>3075</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8773,22 +8773,22 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8808,7 +8808,7 @@
       </c>
       <c r="CX17" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -8825,12 +8825,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>52.072</t>
+          <t>50.507</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8850,17 +8850,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8870,37 +8870,37 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-06-27 00:00:00</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-07 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-07 00:00:00</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-13 00:00:00</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -8910,12 +8910,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -8925,22 +8925,22 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-33.20</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024/11/05</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -8950,7 +8950,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -9000,17 +9000,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -9026,7 +9026,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -9040,47 +9040,47 @@
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>-0.98</v>
+        <v>-0.61</v>
       </c>
       <c r="AV18" t="n">
-        <v>-1.06</v>
+        <v>-1.42</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>41.44</v>
+        <v>41.39</v>
       </c>
       <c r="BA18" t="n">
-        <v>42.27</v>
+        <v>42.22</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>43.29</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-14.25</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>-0.39</v>
+        <v>-0.42</v>
       </c>
       <c r="BE18" t="n">
-        <v>-0.35</v>
+        <v>-0.37</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-136.60</t>
+          <t>-137.95</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9099,43 +9099,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>6791742.917391304</t>
+          <t>7435306.067193676</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>2118083.0</t>
+          <t>2057561.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>2732836.8</v>
+        <v>2419050.6</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>2355995.8</t>
+          <t>2423375.9</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>2171316.48</v>
+        <v>2195699.04</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>376841</t>
+          <t>-4325</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>83273.79138100205</t>
+          <t>74314.87645095764</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>64989.64340212941</t>
+          <t>25040.84433571342</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>2118083.0</t>
+          <t>2057561.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>-31.53</t>
+          <t>-31.62</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>34.62</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>3064</t>
+          <t>3075</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9265,22 +9265,22 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9300,7 +9300,7 @@
       </c>
       <c r="CX18" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -9317,12 +9317,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>40.565</t>
+          <t>52.072</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9332,149 +9332,149 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>40.6</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>4.13</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-0.66</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>15.99</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2025-06-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2024-11-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2024-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>61.2</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>60.7</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>70.8</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>69.7</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>-33.11</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>-12.20</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024/11/05</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>70.7</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2025/07/31</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>58.8</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>2024/11/19</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>69.4</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>2026/01/22</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
           <t>40.7</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>3.55</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>22.82</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>2025/07/31</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>58.8</t>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>2024/11/19</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>69.4</t>
-        </is>
-      </c>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t>2026/01/22</t>
-        </is>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>40.7</t>
-        </is>
-      </c>
       <c r="AI19" t="inlineStr">
         <is>
           <t>2025/12/11</t>
@@ -9492,17 +9492,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -9528,51 +9528,51 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>-1.21</v>
+        <v>-0.98</v>
       </c>
       <c r="AV19" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-1.06</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>41.49</v>
+        <v>41.44</v>
       </c>
       <c r="BA19" t="n">
-        <v>42.33</v>
+        <v>42.27</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>43.29</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-5.01</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>-0.36</v>
+        <v>-0.39</v>
       </c>
       <c r="BE19" t="n">
-        <v>-0.34</v>
+        <v>-0.35</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9581,7 +9581,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-135.57</t>
+          <t>-136.60</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9591,43 +9591,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>6791742.917391304</t>
+          <t>7435306.067193676</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>1655115.0</t>
+          <t>2118083.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>2882296.2</v>
+        <v>2732836.8</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>2346796.6</t>
+          <t>2355995.8</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>2197559.12</v>
+        <v>2171316.48</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>535499</t>
+          <t>376841</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>86598.18192261527</t>
+          <t>83273.79138100205</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>113253.7976612188</t>
+          <t>64989.64340212941</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>1655115.0</t>
+          <t>2118083.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>-31.37</t>
+          <t>-31.53</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -9707,7 +9707,7 @@
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9732,12 +9732,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>34.62</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>3064</t>
+          <t>3075</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9757,22 +9757,22 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9792,14 +9792,14 @@
       </c>
       <c r="CX19" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -9809,12 +9809,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>115.01</t>
+          <t>40.565</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9834,17 +9834,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>22.82</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9854,37 +9854,37 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-06-27 00:00:00</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-07 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-07 00:00:00</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-13 00:00:00</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -9909,22 +9909,22 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-32.95</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024/11/05</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -9934,7 +9934,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9984,17 +9984,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>7.70</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -10020,48 +10020,48 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>14.04</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>-1.35</v>
+        <v>-1.21</v>
       </c>
       <c r="AV20" t="n">
-        <v>-0.16</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>41.45999999999999</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>41.53</v>
+        <v>41.49</v>
       </c>
       <c r="BA20" t="n">
-        <v>42.38</v>
+        <v>42.33</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>-5.01</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>-0.32</v>
+        <v>-0.36</v>
       </c>
       <c r="BE20" t="n">
         <v>-0.34</v>
@@ -10073,7 +10073,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-135.12</t>
+          <t>-135.57</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -10083,43 +10083,43 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>6791742.917391304</t>
+          <t>7435306.067193676</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>4721762.0</t>
+          <t>1655115.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>2997561.4</v>
+        <v>2882296.2</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>2477506.7</t>
+          <t>2346796.6</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>2270637.82</v>
+        <v>2197559.12</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>520054</t>
+          <t>535499</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>81751.70633377827</t>
+          <t>86598.18192261527</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>227761.5252577313</t>
+          <t>113253.7976612188</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>4721762.0</t>
+          <t>1655115.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>-31.03</t>
+          <t>-31.37</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10184,22 +10184,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10224,12 +10224,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>34.62</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>3064</t>
+          <t>3075</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10249,22 +10249,22 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10284,7 +10284,7 @@
       </c>
       <c r="CX20" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -10301,12 +10301,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>37.287</t>
+          <t>115.01</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10326,17 +10326,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10346,37 +10346,37 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-06-27 00:00:00</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-07 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-07 00:00:00</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-13 00:00:00</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -10386,12 +10386,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -10401,22 +10401,22 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-32.62</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024/11/05</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -10426,7 +10426,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10476,17 +10476,17 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>7.70</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10502,58 +10502,58 @@
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>14.04</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>-0.63</v>
+        <v>-1.35</v>
       </c>
       <c r="AV21" t="n">
         <v>-0.16</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>41.51</t>
+          <t>41.45999999999999</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>41.58</v>
+        <v>41.53</v>
       </c>
       <c r="BA21" t="n">
-        <v>42.41</v>
+        <v>42.38</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>43.47</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>14.85</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>-0.29</v>
+        <v>-0.32</v>
       </c>
       <c r="BE21" t="n">
         <v>-0.34</v>
@@ -10565,7 +10565,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-135.52</t>
+          <t>-135.12</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10575,43 +10575,43 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>6791742.917391304</t>
+          <t>7435306.067193676</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>1542732.0</t>
+          <t>4721762.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>2385302.4</v>
+        <v>2997561.4</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>2294484.4</t>
+          <t>2477506.7</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>2236735.98</v>
+        <v>2270637.82</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>90818</t>
+          <t>520054</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>55204.46652942317</t>
+          <t>81751.70633377827</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>54640.33163640229</t>
+          <t>227761.5252577313</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>1542732.0</t>
+          <t>4721762.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10631,7 +10631,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>-30.44</t>
+          <t>-31.03</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>34.62</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>3064</t>
+          <t>3075</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10741,22 +10741,22 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10776,7 +10776,7 @@
       </c>
       <c r="CX21" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -10793,12 +10793,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>86.561</t>
+          <t>37.287</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10818,17 +10818,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10838,37 +10838,37 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-06-27 00:00:00</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-07 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-07 00:00:00</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-13 00:00:00</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -10878,12 +10878,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -10893,22 +10893,22 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-32.04</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024/11/05</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -10918,7 +10918,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10968,17 +10968,17 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10994,24 +10994,24 @@
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>13.16</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>37.72</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>0.22</v>
+        <v>-0.63</v>
       </c>
       <c r="AV22" t="n">
-        <v>-0.33</v>
+        <v>-0.16</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
@@ -11020,35 +11020,35 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>41.45999999999999</t>
+          <t>41.51</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>41.6</v>
+        <v>41.58</v>
       </c>
       <c r="BA22" t="n">
-        <v>42.43</v>
+        <v>42.41</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>43.54</t>
+          <t>43.47</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>14.85</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>-0.28</v>
+        <v>-0.29</v>
       </c>
       <c r="BE22" t="n">
-        <v>-0.36</v>
+        <v>-0.34</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-136.84</t>
+          <t>-135.52</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -11067,43 +11067,43 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>6791742.917391304</t>
+          <t>7435306.067193676</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>3626492.0</t>
+          <t>1542732.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>2427701.2</v>
+        <v>2385302.4</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>2371803.7</t>
+          <t>2294484.4</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>2236811.2</v>
+        <v>2236735.98</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>55897</t>
+          <t>90818</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>55307.03650997241</t>
+          <t>55204.46652942317</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>145983.2574760602</t>
+          <t>54640.33163640229</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>3626492.0</t>
+          <t>1542732.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -11123,7 +11123,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>-29.93</t>
+          <t>-30.44</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11168,7 +11168,7 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
@@ -11178,12 +11178,12 @@
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>34.62</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>3064</t>
+          <t>3075</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11233,22 +11233,22 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>42.45</t>
+          <t>41.55</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>42.45</t>
+          <t>41.55</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11268,7 +11268,7 @@
       </c>
       <c r="CX22" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -11285,12 +11285,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>68.368</t>
+          <t>86.561</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.55</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11310,17 +11310,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-17.20</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11330,37 +11330,37 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-06-27 00:00:00</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-07 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-07 00:00:00</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-11-13 00:00:00</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -11370,12 +11370,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -11385,22 +11385,22 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-31.55</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024/11/05</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11460,17 +11460,17 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11486,61 +11486,61 @@
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>31.58</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>37.72</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>0.43</v>
+        <v>0.22</v>
       </c>
       <c r="AV23" t="n">
-        <v>-0.49</v>
+        <v>-0.33</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>41.45999999999999</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>41.62</v>
+        <v>41.6</v>
       </c>
       <c r="BA23" t="n">
-        <v>42.46</v>
+        <v>42.43</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>43.61</t>
+          <t>43.54</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>20.30</t>
+          <t>20.43</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>-0.3</v>
+        <v>-0.28</v>
       </c>
       <c r="BE23" t="n">
-        <v>-0.37</v>
+        <v>-0.36</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-138.72</t>
+          <t>-136.84</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11559,43 +11559,43 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>6791742.917391304</t>
+          <t>7435306.067193676</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>2865380.0</t>
+          <t>3626492.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>1979154.8</v>
+        <v>2427701.2</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>2390223.5</t>
+          <t>2371803.7</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>2211857.32</v>
+        <v>2236811.2</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>-411068</t>
+          <t>55897</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>38820.45087977464</t>
+          <t>55307.03650997241</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>47999.46376571245</t>
+          <t>145983.2574760602</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>2865380.0</t>
+          <t>3626492.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11615,7 +11615,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>-29.85</t>
+          <t>-29.93</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11675,7 +11675,7 @@
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>34.62</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>3064</t>
+          <t>3075</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11725,22 +11725,22 @@
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>42.45</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>42.45</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.55</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.55</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11760,7 +11760,991 @@
       </c>
       <c r="CX23" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1760</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>-2.31</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>170.283</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>63.7</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>9.80</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025/09/18</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>70.5</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>2025/12/24</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>63.4</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>68.8</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>2025/12/12</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>65.5</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>2025/11/05</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>64.6</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>2025-05-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="AN24" t="inlineStr">
+        <is>
+          <t>-1.88</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>58.33</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr">
+        <is>
+          <t>31.57</t>
+        </is>
+      </c>
+      <c r="AU24" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>-2.12</v>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>-0.99</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>-2.30</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>63.36</t>
+        </is>
+      </c>
+      <c r="AZ24" t="n">
+        <v>64.73</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>65.37</v>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>66.91</t>
+        </is>
+      </c>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>-13.92</t>
+        </is>
+      </c>
+      <c r="BD24" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="BF24" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="BG24" t="inlineStr">
+        <is>
+          <t>-129.21</t>
+        </is>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="BI24" t="inlineStr">
+        <is>
+          <t>40035261.45463918</t>
+        </is>
+      </c>
+      <c r="BJ24" t="inlineStr">
+        <is>
+          <t>10912503.0</t>
+        </is>
+      </c>
+      <c r="BK24" t="n">
+        <v>6082012.6</v>
+      </c>
+      <c r="BL24" t="inlineStr">
+        <is>
+          <t>5539199.3</t>
+        </is>
+      </c>
+      <c r="BM24" t="n">
+        <v>6314109.14</v>
+      </c>
+      <c r="BN24" t="inlineStr">
+        <is>
+          <t>542813</t>
+        </is>
+      </c>
+      <c r="BO24" t="inlineStr">
+        <is>
+          <t>-73849.03909094637</t>
+        </is>
+      </c>
+      <c r="BP24" t="inlineStr">
+        <is>
+          <t>361830.4726555534</t>
+        </is>
+      </c>
+      <c r="BQ24" t="inlineStr">
+        <is>
+          <t>10912503.0</t>
+        </is>
+      </c>
+      <c r="BR24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS24" t="inlineStr">
+        <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="BT24" t="inlineStr">
+        <is>
+          <t>2025/12/19</t>
+        </is>
+      </c>
+      <c r="BU24" t="inlineStr">
+        <is>
+          <t>-0.47</t>
+        </is>
+      </c>
+      <c r="BV24" t="inlineStr">
+        <is>
+          <t>寶齡富錦</t>
+        </is>
+      </c>
+      <c r="BW24" t="inlineStr">
+        <is>
+          <t>寶齡富錦</t>
+        </is>
+      </c>
+      <c r="BX24" t="inlineStr">
+        <is>
+          <t>生技醫療業</t>
+        </is>
+      </c>
+      <c r="BY24" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BZ24" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="CA24" t="inlineStr">
+        <is>
+          <t>-22.55378299170716</t>
+        </is>
+      </c>
+      <c r="CB24" t="inlineStr">
+        <is>
+          <t>14.88387829883942</t>
+        </is>
+      </c>
+      <c r="CC24" t="inlineStr">
+        <is>
+          <t>1.662704561635163</t>
+        </is>
+      </c>
+      <c r="CD24" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE24" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CF24" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="CG24" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="CH24" t="inlineStr">
+        <is>
+          <t>6.20</t>
+        </is>
+      </c>
+      <c r="CI24" t="inlineStr">
+        <is>
+          <t>31.38</t>
+        </is>
+      </c>
+      <c r="CJ24" t="inlineStr">
+        <is>
+          <t>56.45%</t>
+        </is>
+      </c>
+      <c r="CK24" t="inlineStr">
+        <is>
+          <t>18.71%</t>
+        </is>
+      </c>
+      <c r="CL24" t="inlineStr">
+        <is>
+          <t>58.04</t>
+        </is>
+      </c>
+      <c r="CM24" t="inlineStr">
+        <is>
+          <t>5462</t>
+        </is>
+      </c>
+      <c r="CN24" t="inlineStr">
+        <is>
+          <t>藥品38.92%、權利金收入20.27%、食品17.41%、化工8.69%、原料藥(API)8.12%、檢驗試劑5.07%、里程金1.10%、醫美醫材0.43% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO24" t="inlineStr">
+        <is>
+          <t>寶齡富錦-生技醫療業-上市</t>
+        </is>
+      </c>
+      <c r="CP24" t="inlineStr">
+        <is>
+          <t>生技醫療業右下上市</t>
+        </is>
+      </c>
+      <c r="CQ24" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="CR24" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="CS24" t="inlineStr">
+        <is>
+          <t>63.6</t>
+        </is>
+      </c>
+      <c r="CT24" t="inlineStr">
+        <is>
+          <t>63.7</t>
+        </is>
+      </c>
+      <c r="CU24" t="inlineStr">
+        <is>
+          <t>22.18</t>
+        </is>
+      </c>
+      <c r="CV24" t="inlineStr">
+        <is>
+          <t>** 石化及塑橡膠 - 化妝品** 製藥 - 中、西藥製劑、藥品代理銷售及通路** 食品生技 - 加工製成品、保健食品代理銷售及通路** 醫療器材 - 醫療耗材、生物檢測</t>
+        </is>
+      </c>
+      <c r="CW24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CX24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1737</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>-0.32</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>81.467</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>31.5</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>4.84</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2025-08-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2025-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>2025-07-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2025-07-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>33.05</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>32.25</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>32.9</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>32.75</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>-2.33</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025/02/21</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>32.7</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>2025/08/28</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>32.2</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>2025/04/08</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>30.65</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>31.6</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>31.6</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>2025-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>8.01</t>
+        </is>
+      </c>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>-0.16</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>14.29</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr">
+        <is>
+          <t>42.86</t>
+        </is>
+      </c>
+      <c r="AU25" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>-0.4</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>-0.49</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>31.64</t>
+        </is>
+      </c>
+      <c r="AZ25" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>31.72</v>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>31.88</t>
+        </is>
+      </c>
+      <c r="BC25" t="inlineStr">
+        <is>
+          <t>25.55</t>
+        </is>
+      </c>
+      <c r="BD25" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="BF25" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="BG25" t="inlineStr">
+        <is>
+          <t>-114.07</t>
+        </is>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2025/12/19</t>
+        </is>
+      </c>
+      <c r="BI25" t="inlineStr">
+        <is>
+          <t>11320400.26082474</t>
+        </is>
+      </c>
+      <c r="BJ25" t="inlineStr">
+        <is>
+          <t>2568418.0</t>
+        </is>
+      </c>
+      <c r="BK25" t="n">
+        <v>3289054.2</v>
+      </c>
+      <c r="BL25" t="inlineStr">
+        <is>
+          <t>3137217.9</t>
+        </is>
+      </c>
+      <c r="BM25" t="n">
+        <v>3324051.1</v>
+      </c>
+      <c r="BN25" t="inlineStr">
+        <is>
+          <t>151836</t>
+        </is>
+      </c>
+      <c r="BO25" t="inlineStr">
+        <is>
+          <t>-3853.900231664111</t>
+        </is>
+      </c>
+      <c r="BP25" t="inlineStr">
+        <is>
+          <t>32790.85744653689</t>
+        </is>
+      </c>
+      <c r="BQ25" t="inlineStr">
+        <is>
+          <t>2568418.0</t>
+        </is>
+      </c>
+      <c r="BR25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS25" t="inlineStr">
+        <is>
+          <t>32.7</t>
+        </is>
+      </c>
+      <c r="BT25" t="inlineStr">
+        <is>
+          <t>2025/05/19</t>
+        </is>
+      </c>
+      <c r="BU25" t="inlineStr">
+        <is>
+          <t>-3.67</t>
+        </is>
+      </c>
+      <c r="BV25" t="inlineStr">
+        <is>
+          <t>臺鹽</t>
+        </is>
+      </c>
+      <c r="BW25" t="inlineStr">
+        <is>
+          <t>臺鹽</t>
+        </is>
+      </c>
+      <c r="BX25" t="inlineStr">
+        <is>
+          <t>食品工業</t>
+        </is>
+      </c>
+      <c r="BY25" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BZ25" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="CA25" t="inlineStr">
+        <is>
+          <t>11.30964198266164</t>
+        </is>
+      </c>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t>7.950770160072485</t>
+        </is>
+      </c>
+      <c r="CC25" t="inlineStr">
+        <is>
+          <t>2.099499961706554</t>
+        </is>
+      </c>
+      <c r="CD25" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE25" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CF25" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="CG25" t="inlineStr">
+        <is>
+          <t>4.13</t>
+        </is>
+      </c>
+      <c r="CH25" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
+      </c>
+      <c r="CI25" t="inlineStr">
+        <is>
+          <t>18.86</t>
+        </is>
+      </c>
+      <c r="CJ25" t="inlineStr">
+        <is>
+          <t>39.76%</t>
+        </is>
+      </c>
+      <c r="CK25" t="inlineStr">
+        <is>
+          <t>11.78%</t>
+        </is>
+      </c>
+      <c r="CL25" t="inlineStr">
+        <is>
+          <t>25.33</t>
+        </is>
+      </c>
+      <c r="CM25" t="inlineStr">
+        <is>
+          <t>6300</t>
+        </is>
+      </c>
+      <c r="CN25" t="inlineStr">
+        <is>
+          <t>鹽46.50%、包裝飲用水34.02%、清潔用品5.33%、保健食品5.08%、美容保養品4.12%、工程及勞務2.55%、其他2.39% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO25" t="inlineStr">
+        <is>
+          <t>臺鹽-食品工業-上市</t>
+        </is>
+      </c>
+      <c r="CP25" t="inlineStr">
+        <is>
+          <t>食品工業右下上市</t>
+        </is>
+      </c>
+      <c r="CQ25" t="inlineStr">
+        <is>
+          <t>31.6</t>
+        </is>
+      </c>
+      <c r="CR25" t="inlineStr">
+        <is>
+          <t>31.6</t>
+        </is>
+      </c>
+      <c r="CS25" t="inlineStr">
+        <is>
+          <t>31.45</t>
+        </is>
+      </c>
+      <c r="CT25" t="inlineStr">
+        <is>
+          <t>31.5</t>
+        </is>
+      </c>
+      <c r="CU25" t="inlineStr">
+        <is>
+          <t>33.23</t>
+        </is>
+      </c>
+      <c r="CV25" t="inlineStr">
+        <is>
+          <t>** 食品 - 原物料、營養食品** 石化及塑橡膠 - 化妝品</t>
+        </is>
+      </c>
+      <c r="CW25" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CX25" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
     </row>

--- a/Result/checksun_type/化妝品.xlsx
+++ b/Result/checksun_type/化妝品.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CX25"/>
+  <dimension ref="A1:CX27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -953,12 +953,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4190.357</t>
+          <t>1141.159</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -983,12 +983,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>87.93</t>
+          <t>71.76</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1128,154 +1128,154 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>12.70</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>4190</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>37.14</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>-3.06</v>
+        <v>-3.92</v>
       </c>
       <c r="AV2" t="n">
-        <v>6.94</v>
+        <v>5.75</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
+          <t>17.85</t>
+        </is>
+      </c>
+      <c r="AZ2" t="n">
+        <v>16.88</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>16.76</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>16.81</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>49.59</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>0.87</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>-80.69</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>2026/01/27</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>69013672.0147929</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>19490112.0</t>
+        </is>
+      </c>
+      <c r="BK2" t="n">
+        <v>100189358.4</v>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>58331108.3</t>
+        </is>
+      </c>
+      <c r="BM2" t="n">
+        <v>15415758.92</v>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>41858250</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>9816999.517420726</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>11594304.76359032</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>19490112.0</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
           <t>18.0</t>
         </is>
       </c>
-      <c r="AZ2" t="n">
-        <v>16.83</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>16.74</v>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>16.81</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>89.01</t>
-        </is>
-      </c>
-      <c r="BD2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>0.87</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>-83.08</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>2026/01/27</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>69092285.6590909</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>74227869.0</t>
-        </is>
-      </c>
-      <c r="BK2" t="n">
-        <v>107145825</v>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>57014855.3</t>
-        </is>
-      </c>
-      <c r="BM2" t="n">
-        <v>15184901.32</v>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>50130969</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>9493853.109026255</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>17859478.60877223</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>74227869.0</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
       <c r="BT2" t="inlineStr">
         <is>
           <t>2026/01/29</t>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1328,22 +1328,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>34.62</t>
+          <t>34.68</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3350</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1393,22 +1393,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>9.0</t>
         </is>
       </c>
     </row>
@@ -1445,12 +1445,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-5.65</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2904.755</t>
+          <t>4190.357</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1470,17 +1470,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>87.56</t>
+          <t>87.93</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1620,17 +1620,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>12.70</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1641,50 +1641,50 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>4190</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>37.14</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>59.05</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>-4.33</v>
+        <v>-3.06</v>
       </c>
       <c r="AV3" t="n">
-        <v>5.93</v>
+        <v>6.94</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>17.77</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>16.77</v>
+        <v>16.83</v>
       </c>
       <c r="BA3" t="n">
-        <v>16.72</v>
+        <v>16.74</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
@@ -1693,14 +1693,14 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>142.98</t>
+          <t>89.01</t>
         </is>
       </c>
       <c r="BD3" t="n">
         <v>0.28</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-86.85</t>
+          <t>-83.08</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1719,43 +1719,43 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>69092285.6590909</t>
+          <t>69013672.0147929</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>50050807.0</t>
+          <t>74227869.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>95018011.2</v>
+        <v>107145825</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>50659715.5</t>
+          <t>57014855.3</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>13784987.5</v>
+        <v>15184901.32</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>44358295</t>
+          <t>50130969</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>7972830.290890622</t>
+          <t>9493853.109026255</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>20307128.75871883</t>
+          <t>17859478.60877223</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>50050807.0</t>
+          <t>74227869.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1860,12 +1860,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>34.62</t>
+          <t>34.68</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3350</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1885,22 +1885,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9.0</t>
         </is>
       </c>
     </row>
@@ -1937,12 +1937,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-7.69</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>14269.838</t>
+          <t>2904.755</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1962,17 +1962,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>85.38</t>
+          <t>87.56</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2112,17 +2112,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>43.24</t>
+          <t>8.80</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-17.76</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2133,50 +2133,50 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>4190</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>52.86</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>84.29</t>
+          <t>59.05</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>2.27</v>
+        <v>-4.33</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.04</v>
+        <v>5.93</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.77</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>16.76</v>
+        <v>16.77</v>
       </c>
       <c r="BA4" t="n">
-        <v>16.7</v>
+        <v>16.72</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
@@ -2185,14 +2185,14 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>334.39</t>
+          <t>142.98</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>0.32</v>
+        <v>0.28</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-91.55</t>
+          <t>-86.85</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2211,43 +2211,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>69092285.6590909</t>
+          <t>69013672.0147929</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>271794825.0</t>
+          <t>50050807.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>85900227.8</v>
+        <v>95018011.2</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>46337047.2</t>
+          <t>50659715.5</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>13077653.86</v>
+        <v>13784987.5</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>39563180</t>
+          <t>44358295</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>5730230.569467312</t>
+          <t>7972830.290890622</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>25668916.73154542</t>
+          <t>20307128.75871883</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>271794825.0</t>
+          <t>50050807.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2312,22 +2312,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>34.62</t>
+          <t>34.68</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3350</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2377,22 +2377,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10.0</t>
         </is>
       </c>
     </row>
@@ -2429,12 +2429,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>8.91</t>
+          <t>-7.69</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4345.538</t>
+          <t>14269.838</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2454,17 +2454,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-12.61</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>66.07</t>
+          <t>85.38</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2604,87 +2604,87 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>13.17</t>
+          <t>43.24</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-17.76</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>4190</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>52.86</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>84.29</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>13.98</v>
+        <v>2.27</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.39</v>
+        <v>5.04</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>16.68</v>
+        <v>16.76</v>
       </c>
       <c r="BA5" t="n">
-        <v>16.68</v>
+        <v>16.7</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>2107.80</t>
+          <t>334.39</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>0.27</v>
+        <v>0.32</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-98.61</t>
+          <t>-91.55</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2703,43 +2703,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>69092285.6590909</t>
+          <t>69013672.0147929</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>85383179.0</t>
+          <t>271794825.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>32469406.2</v>
+        <v>85900227.8</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>19551967.8</t>
+          <t>46337047.2</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>7775541.34</v>
+        <v>13077653.86</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>12917438</t>
+          <t>39563180</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>2105014.903634928</t>
+          <t>5730230.569467312</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>8653579.166599646</t>
+          <t>25668916.73154542</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>85383179.0</t>
+          <t>271794825.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>9.17</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2804,22 +2804,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>34.62</t>
+          <t>34.68</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3350</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2869,22 +2869,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2904,14 +2904,14 @@
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10.0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>8.91</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3052.112</t>
+          <t>4345.538</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2946,17 +2946,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-14.58</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>43.47</t>
+          <t>66.07</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3096,17 +3096,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>9.25</t>
+          <t>13.17</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3117,12 +3117,12 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>4190</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -3132,51 +3132,51 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>8.029999999999999</v>
+        <v>13.98</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.3</v>
+        <v>3.39</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>16.57</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>16.52</v>
+        <v>16.68</v>
       </c>
       <c r="BA6" t="n">
-        <v>16.62</v>
+        <v>16.68</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>153.51</t>
+          <t>2107.80</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>0.03</v>
+        <v>0.27</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-105.92</t>
+          <t>-98.61</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3195,43 +3195,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>69092285.6590909</t>
+          <t>69013672.0147929</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>54272445.0</t>
+          <t>85383179.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>16472858.2</v>
+        <v>32469406.2</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>11482077.0</t>
+          <t>19551967.8</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>6145777.4</v>
+        <v>7775541.34</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>4990781</t>
+          <t>12917438</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>914366.8558231613</t>
+          <t>2105014.903634928</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>4009574.032155704</t>
+          <t>8653579.166599646</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>54272445.0</t>
+          <t>85383179.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>9.17</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>34.62</t>
+          <t>34.68</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3350</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3361,22 +3361,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3396,14 +3396,14 @@
       </c>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10.0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>827.557</t>
+          <t>3052.112</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3438,17 +3438,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>43.47</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3588,17 +3588,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>9.25</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>5.60</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3609,66 +3609,66 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>4190</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>0.37</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="AV7" t="n">
-        <v>-1.31</v>
+        <v>0.3</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>16.24</t>
+          <t>16.57</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>16.45</v>
+        <v>16.52</v>
       </c>
       <c r="BA7" t="n">
-        <v>16.6</v>
+        <v>16.62</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>16.77</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-40.86</t>
+          <t>153.51</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>-0.1</v>
+        <v>0.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.05</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-108.19</t>
+          <t>-105.92</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3687,43 +3687,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>69092285.6590909</t>
+          <t>69013672.0147929</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>13588800.0</t>
+          <t>54272445.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>6883885.6</v>
+        <v>16472858.2</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>6630741.6</t>
+          <t>11482077.0</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>5332397.1</v>
+        <v>6145777.4</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>253144</t>
+          <t>4990781</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>351601.9146717899</t>
+          <t>914366.8558231613</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>565374.8389445115</t>
+          <t>4009574.032155704</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>13588800.0</t>
+          <t>54272445.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>-9.44</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3788,22 +3788,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>34.62</t>
+          <t>34.68</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3350</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3853,22 +3853,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="CX7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10.0</t>
         </is>
       </c>
     </row>
@@ -3905,12 +3905,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>275.868</t>
+          <t>827.557</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>16.15</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3930,17 +3930,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>7.45</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4080,17 +4080,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4101,66 +4101,66 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>4190</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-0.68</v>
+        <v>0.37</v>
       </c>
       <c r="AV8" t="n">
-        <v>-1.26</v>
+        <v>-1.31</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>16.24</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>16.47</v>
+        <v>16.45</v>
       </c>
       <c r="BA8" t="n">
-        <v>16.61</v>
+        <v>16.6</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>16.77</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-56.60</t>
+          <t>-40.86</t>
         </is>
       </c>
       <c r="BD8" t="n">
         <v>-0.1</v>
       </c>
       <c r="BE8" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-107.35</t>
+          <t>-108.19</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4179,43 +4179,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>69092285.6590909</t>
+          <t>69013672.0147929</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>4461890.0</t>
+          <t>13588800.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>6301419.8</v>
+        <v>6883885.6</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>6577320.7</t>
+          <t>6630741.6</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>5097733.74</v>
+        <v>5332397.1</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-275900</t>
+          <t>253144</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>312734.1102585678</t>
+          <t>351601.9146717899</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-16139.71703378018</t>
+          <t>565374.8389445115</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>4461890.0</t>
+          <t>13588800.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>-10.28</t>
+          <t>-9.44</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>34.62</t>
+          <t>34.68</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3350</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4350,17 +4350,17 @@
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>16.35</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>16.15</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>16.15</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="CX8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10.0</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>285.969</t>
+          <t>275.868</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>16.15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4422,17 +4422,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4572,17 +4572,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4593,12 +4593,12 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>4190</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4612,44 +4612,44 @@
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-0.92</v>
+        <v>-0.68</v>
       </c>
       <c r="AV9" t="n">
-        <v>-0.85</v>
+        <v>-1.26</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>16.35</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>16.49</v>
+        <v>16.47</v>
       </c>
       <c r="BA9" t="n">
-        <v>16.62</v>
+        <v>16.61</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-51.70</t>
+          <t>-56.60</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>-0.08</v>
+        <v>-0.1</v>
       </c>
       <c r="BE9" t="n">
         <v>-0.06</v>
@@ -4661,7 +4661,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-106.31</t>
+          <t>-107.35</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4671,43 +4671,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>69092285.6590909</t>
+          <t>69013672.0147929</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>4640717.0</t>
+          <t>4461890.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>6773866.6</v>
+        <v>6301419.8</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>6953049.8</t>
+          <t>6577320.7</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>5099505.8</v>
+        <v>5097733.74</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-179183</t>
+          <t>-275900</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>372529.3515844492</t>
+          <t>312734.1102585678</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>131584.8357484369</t>
+          <t>-16139.71703378018</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>4640717.0</t>
+          <t>4461890.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>-10.00</t>
+          <t>-10.28</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>34.62</t>
+          <t>34.68</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3350</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4837,14 +4837,14 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
           <t>16.35</t>
         </is>
       </c>
-      <c r="CR9" t="inlineStr">
-        <is>
-          <t>16.35</t>
-        </is>
-      </c>
       <c r="CS9" t="inlineStr">
         <is>
           <t>16.15</t>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>16.15</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="CX9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>9.0</t>
         </is>
       </c>
     </row>
@@ -4889,12 +4889,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>332.074</t>
+          <t>285.969</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4914,17 +4914,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -5064,17 +5064,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5085,66 +5085,66 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>4190</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="AU10" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="AV10" t="n">
         <v>-0.85</v>
       </c>
-      <c r="AV10" t="n">
-        <v>-0.47</v>
-      </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>16.44</t>
+          <t>16.35</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>16.52</v>
+        <v>16.49</v>
       </c>
       <c r="BA10" t="n">
-        <v>16.63</v>
+        <v>16.62</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-37.24</t>
+          <t>-51.70</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="BE10" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-105.50</t>
+          <t>-106.31</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5163,43 +5163,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>69092285.6590909</t>
+          <t>69013672.0147929</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>5400439.0</t>
+          <t>4640717.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>6634529.4</v>
+        <v>6773866.6</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>6936334.7</t>
+          <t>6953049.8</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>5081502.14</v>
+        <v>5099505.8</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-301805</t>
+          <t>-179183</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>416337.4453728151</t>
+          <t>372529.3515844492</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>318760.4170177318</t>
+          <t>131584.8357484369</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>5400439.0</t>
+          <t>4640717.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>-9.44</t>
+          <t>-10.00</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>34.62</t>
+          <t>34.68</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3350</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>16.35</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
@@ -5339,14 +5339,14 @@
       </c>
       <c r="CS10" t="inlineStr">
         <is>
+          <t>16.15</t>
+        </is>
+      </c>
+      <c r="CT10" t="inlineStr">
+        <is>
           <t>16.2</t>
         </is>
       </c>
-      <c r="CT10" t="inlineStr">
-        <is>
-          <t>16.3</t>
-        </is>
-      </c>
       <c r="CU10" t="inlineStr">
         <is>
           <t>11.58</t>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="CX10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>9.0</t>
         </is>
       </c>
     </row>
@@ -5381,12 +5381,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>388.233</t>
+          <t>332.074</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5396,149 +5396,149 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>16.3</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4.96</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-4.35</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025/10/17</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17.1</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>16.95</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>17.8</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>2026/01/20</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
           <t>16.25</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>6.88</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-9.80</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2025/10/17</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>17.1</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2025/11/06</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>16.95</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>2025/07/07</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>17.8</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>2026/01/20</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>16.25</t>
-        </is>
-      </c>
       <c r="AI11" t="inlineStr">
         <is>
           <t>2025/12/26</t>
@@ -5556,17 +5556,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5577,67 +5577,67 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>4190</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>-1.69</v>
+        <v>-0.85</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0.06</v>
+        <v>-0.47</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>16.53</t>
+          <t>16.44</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>16.54</v>
+        <v>16.52</v>
       </c>
       <c r="BA11" t="n">
-        <v>16.64</v>
+        <v>16.63</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-20.44</t>
+          <t>-37.24</t>
         </is>
       </c>
       <c r="BD11" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="BE11" t="n">
         <v>-0.05</v>
       </c>
-      <c r="BE11" t="n">
-        <v>-0.04</v>
-      </c>
       <c r="BF11" t="inlineStr">
         <is>
           <t>0.87</t>
@@ -5645,7 +5645,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-104.99</t>
+          <t>-105.50</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5655,43 +5655,43 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>69092285.6590909</t>
+          <t>69013672.0147929</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>6327582.0</t>
+          <t>5400439.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>6491295.8</v>
+        <v>6634529.4</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>7196752.8</t>
+          <t>6936334.7</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>5141183.88</v>
+        <v>5081502.14</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-705457</t>
+          <t>-301805</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>434078.7232555575</t>
+          <t>416337.4453728151</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>493371.0182232345</t>
+          <t>318760.4170177318</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>6327582.0</t>
+          <t>5400439.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>-9.72</t>
+          <t>-9.44</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>34.62</t>
+          <t>34.68</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3350</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5821,22 +5821,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>16.25</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>16.35</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>16.25</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>16.25</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5856,14 +5856,14 @@
       </c>
       <c r="CX11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>9.0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5873,12 +5873,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>648.754</t>
+          <t>388.233</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>16.25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5898,17 +5898,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-10.37</t>
+          <t>-9.80</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -6048,17 +6048,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6069,63 +6069,63 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>4190</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>50.93</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>-1.32</v>
+        <v>-1.69</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.36</v>
+        <v>-0.06</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>16.62</t>
+          <t>16.53</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>16.56</v>
+        <v>16.54</v>
       </c>
       <c r="BA12" t="n">
-        <v>16.65</v>
+        <v>16.64</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>16.83</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>28.78</t>
+          <t>-20.44</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>-0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="BE12" t="n">
         <v>-0.04</v>
@@ -6137,7 +6137,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-104.73</t>
+          <t>-104.99</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6147,43 +6147,43 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>69092285.6590909</t>
+          <t>69013672.0147929</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>10676471.0</t>
+          <t>6327582.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>6377597.6</v>
+        <v>6491295.8</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>7115866.6</t>
+          <t>7196752.8</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>5160002.2</v>
+        <v>5141183.88</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-738269</t>
+          <t>-705457</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>423298.3059887072</t>
+          <t>434078.7232555575</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>625857.5907231215</t>
+          <t>493371.0182232345</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>10676471.0</t>
+          <t>6327582.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>-8.89</t>
+          <t>-9.72</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -6288,12 +6288,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>34.62</t>
+          <t>34.68</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3350</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6313,22 +6313,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.25</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>16.35</t>
+          <t>16.25</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>16.25</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="CX12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>9.0</t>
         </is>
       </c>
     </row>
@@ -6365,12 +6365,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>226.35</t>
+          <t>267.325</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>85.50</t>
+          <t>48.46</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-30.23</t>
+          <t>-30.31</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -6490,7 +6490,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6540,17 +6540,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>17.91</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6561,66 +6561,66 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>-4.81</v>
+        <v>-3.93</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.5</v>
+        <v>4.36</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>44.49</t>
+          <t>44.03</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>42.17</v>
+        <v>42.19</v>
       </c>
       <c r="BA13" t="n">
-        <v>42.39</v>
+        <v>42.38</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>43.22</t>
+          <t>43.18</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>167.39</t>
+          <t>76.88</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>0.38</v>
+        <v>0.31</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
@@ -6629,7 +6629,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-85.25</t>
+          <t>-81.74</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6639,43 +6639,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>7435306.067193676</t>
+          <t>7453881.860946746</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>9926503.0</t>
+          <t>11235489.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>30954151</v>
+        <v>26211444.6</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>16686600.8</t>
+          <t>17655876.5</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>5067898.96</v>
+        <v>5273864.44</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>14267550</t>
+          <t>8555568</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>2727067.001083214</t>
+          <t>2719001.516642336</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>3706873.146931395</t>
+          <t>2674641.352217507</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>9926503.0</t>
+          <t>11235489.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>-28.58</t>
+          <t>-28.67</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
@@ -6780,12 +6780,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>34.62</t>
+          <t>34.68</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>3071</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6805,22 +6805,22 @@
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="CX13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10.0</t>
         </is>
       </c>
     </row>
@@ -6857,12 +6857,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>197.457</t>
+          <t>226.35</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6882,17 +6882,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>82.98</t>
+          <t>85.50</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-30.48</t>
+          <t>-30.23</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -7032,17 +7032,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>13.23</t>
+          <t>15.16</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -7053,66 +7053,66 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>19.41</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>54.31</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>-4.37</v>
+        <v>-4.81</v>
       </c>
       <c r="AV14" t="n">
-        <v>4.72</v>
+        <v>5.5</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>44.13</t>
+          <t>44.49</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>42.14</v>
+        <v>42.17</v>
       </c>
       <c r="BA14" t="n">
-        <v>42.4</v>
+        <v>42.39</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>43.26</t>
+          <t>43.22</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>453.26</t>
+          <t>167.39</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>0.46</v>
+        <v>0.38</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-91.42</t>
+          <t>-85.25</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7131,43 +7131,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>7435306.067193676</t>
+          <t>7453881.860946746</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>8413534.0</t>
+          <t>9926503.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>29380362.6</v>
+        <v>30954151</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>16056599.7</t>
+          <t>16686600.8</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>4904141.1</v>
+        <v>5067898.96</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>13323762</t>
+          <t>14267550</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>2548920.429110818</t>
+          <t>2727067.001083214</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>5189350.169846542</t>
+          <t>3706873.146931395</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>8413534.0</t>
+          <t>9926503.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>-28.84</t>
+          <t>-28.58</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>34.62</t>
+          <t>34.68</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>3071</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7297,22 +7297,22 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>44.15</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>44.15</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7332,7 +7332,7 @@
       </c>
       <c r="CX14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>9.0</t>
         </is>
       </c>
     </row>
@@ -7349,12 +7349,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1195.571</t>
+          <t>197.457</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7374,17 +7374,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>81.41</t>
+          <t>82.98</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7449,7 +7449,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-27.10</t>
+          <t>-30.48</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7524,17 +7524,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>80.08</t>
+          <t>13.23</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>-19.10</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7545,66 +7545,66 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>43.53</t>
+          <t>19.41</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>81.18</t>
+          <t>54.31</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>1</v>
+        <v>-4.37</v>
       </c>
       <c r="AV15" t="n">
-        <v>4.09</v>
+        <v>4.72</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>43.81</t>
+          <t>44.13</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>42.09</v>
+        <v>42.14</v>
       </c>
       <c r="BA15" t="n">
         <v>42.4</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>43.29</t>
+          <t>43.26</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>5229.05</t>
+          <t>453.26</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>0.57</v>
+        <v>0.46</v>
       </c>
       <c r="BE15" t="n">
-        <v>-0.01</v>
+        <v>0.08</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-101.14</t>
+          <t>-91.42</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7623,43 +7623,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>7435306.067193676</t>
+          <t>7453881.860946746</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>56593114.0</t>
+          <t>8413534.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>28121272.4</v>
+        <v>29380362.6</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>15501784.3</t>
+          <t>16056599.7</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>4746863</v>
+        <v>4904141.1</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>12619488</t>
+          <t>13323762</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>2068842.294431595</t>
+          <t>2548920.429110818</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>7283944.37508795</t>
+          <t>5189350.169846542</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>56593114.0</t>
+          <t>8413534.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>-25.38</t>
+          <t>-28.84</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7724,17 +7724,17 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>34.62</t>
+          <t>34.68</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>3071</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7789,22 +7789,22 @@
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>44.15</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>44.15</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>44.15</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7824,7 +7824,7 @@
       </c>
       <c r="CX15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>9.0</t>
         </is>
       </c>
     </row>
@@ -7841,12 +7841,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>924.579</t>
+          <t>1195.571</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7866,17 +7866,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-15.82</t>
+          <t>-4.61</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>81.41</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-19.19</t>
+          <t>-27.10</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -8016,17 +8016,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>61.93</t>
+          <t>80.08</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>-19.10</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -8037,66 +8037,66 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>43.53</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>81.18</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>13.81</v>
+        <v>1</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.74</v>
+        <v>4.09</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.81</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>41.95</v>
+        <v>42.09</v>
       </c>
       <c r="BA16" t="n">
-        <v>42.35</v>
+        <v>42.4</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>43.31</t>
+          <t>43.29</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>413.12</t>
+          <t>5229.05</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>0.49</v>
+        <v>0.57</v>
       </c>
       <c r="BE16" t="n">
-        <v>-0.16</v>
+        <v>-0.01</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-116.07</t>
+          <t>-101.14</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8115,43 +8115,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>7435306.067193676</t>
+          <t>7453881.860946746</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>44888583.0</t>
+          <t>56593114.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>17133672.6</v>
+        <v>28121272.4</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>10065617.0</t>
+          <t>15501784.3</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>3634806.6</v>
+        <v>4746863</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>7068055</t>
+          <t>12619488</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>1120641.91613044</t>
+          <t>2068842.294431595</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>4853983.083465392</t>
+          <t>7283944.37508795</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>44888583.0</t>
+          <t>56593114.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8171,7 +8171,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>-17.28</t>
+          <t>-25.38</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8216,17 +8216,17 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>34.62</t>
+          <t>34.68</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>3071</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8281,22 +8281,22 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>44.15</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8316,14 +8316,14 @@
       </c>
       <c r="CX16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>9.0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -8333,12 +8333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>789.819</t>
+          <t>924.579</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8358,17 +8358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-15.96</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>58.46</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8433,7 +8433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-26.52</t>
+          <t>-19.19</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8508,17 +8508,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>52.90</t>
+          <t>61.93</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>7.21</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8529,12 +8529,12 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -8544,51 +8544,51 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>7.55</v>
+        <v>13.81</v>
       </c>
       <c r="AV17" t="n">
-        <v>-0.22</v>
+        <v>2.74</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>41.47000000000001</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>41.56</v>
+        <v>41.95</v>
       </c>
       <c r="BA17" t="n">
-        <v>42.22</v>
+        <v>42.35</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.31</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>64.79</t>
+          <t>413.12</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>-0.11</v>
+        <v>0.49</v>
       </c>
       <c r="BE17" t="n">
-        <v>-0.32</v>
+        <v>-0.16</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-132.66</t>
+          <t>-116.07</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8607,43 +8607,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>7435306.067193676</t>
+          <t>7453881.860946746</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>34949021.0</t>
+          <t>44888583.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>9100308.4</v>
+        <v>17133672.6</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>5742805.4</t>
+          <t>10065617.0</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>2789036.3</v>
+        <v>3634806.6</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>3357503</t>
+          <t>7068055</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>441852.6129786303</t>
+          <t>1120641.91613044</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>2463310.16388083</t>
+          <t>4853983.083465392</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>34949021.0</t>
+          <t>44888583.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8663,7 +8663,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>-24.79</t>
+          <t>-17.28</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8708,7 +8708,7 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>34.62</t>
+          <t>34.68</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>3071</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8773,22 +8773,22 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8808,14 +8808,14 @@
       </c>
       <c r="CX17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9.0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>50.507</t>
+          <t>789.819</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8850,17 +8850,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>-5.44</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>58.46</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8925,7 +8925,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-33.20</t>
+          <t>-26.52</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -8950,7 +8950,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -9000,17 +9000,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>52.90</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>7.21</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -9021,47 +9021,47 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>-0.61</v>
+        <v>7.55</v>
       </c>
       <c r="AV18" t="n">
-        <v>-1.42</v>
+        <v>-0.22</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>41.47000000000001</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>41.39</v>
+        <v>41.56</v>
       </c>
       <c r="BA18" t="n">
         <v>42.22</v>
@@ -9073,14 +9073,14 @@
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-14.25</t>
+          <t>64.79</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>-0.42</v>
+        <v>-0.11</v>
       </c>
       <c r="BE18" t="n">
-        <v>-0.37</v>
+        <v>-0.32</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-137.95</t>
+          <t>-132.66</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9099,43 +9099,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>7435306.067193676</t>
+          <t>7453881.860946746</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>2057561.0</t>
+          <t>34949021.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>2419050.6</v>
+        <v>9100308.4</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>2423375.9</t>
+          <t>5742805.4</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>2195699.04</v>
+        <v>2789036.3</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>-4325</t>
+          <t>3357503</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>74314.87645095764</t>
+          <t>441852.6129786303</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>25040.84433571342</t>
+          <t>2463310.16388083</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>2057561.0</t>
+          <t>34949021.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>-31.62</t>
+          <t>-24.79</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9200,17 +9200,17 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>34.62</t>
+          <t>34.68</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>3071</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9265,22 +9265,22 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9300,7 +9300,7 @@
       </c>
       <c r="CX18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10.0</t>
         </is>
       </c>
     </row>
@@ -9317,12 +9317,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>52.072</t>
+          <t>50.507</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9332,7 +9332,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9342,17 +9342,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-33.11</t>
+          <t>-33.20</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9492,17 +9492,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9513,12 +9513,12 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -9532,47 +9532,47 @@
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>-0.98</v>
+        <v>-0.61</v>
       </c>
       <c r="AV19" t="n">
-        <v>-1.06</v>
+        <v>-1.42</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>41.44</v>
+        <v>41.39</v>
       </c>
       <c r="BA19" t="n">
-        <v>42.27</v>
+        <v>42.22</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>43.29</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-14.25</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>-0.39</v>
+        <v>-0.42</v>
       </c>
       <c r="BE19" t="n">
-        <v>-0.35</v>
+        <v>-0.37</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9581,7 +9581,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-136.60</t>
+          <t>-137.95</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9591,43 +9591,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>7435306.067193676</t>
+          <t>7453881.860946746</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>2118083.0</t>
+          <t>2057561.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>2732836.8</v>
+        <v>2419050.6</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>2355995.8</t>
+          <t>2423375.9</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>2171316.48</v>
+        <v>2195699.04</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>376841</t>
+          <t>-4325</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>83273.79138100205</t>
+          <t>74314.87645095764</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>64989.64340212941</t>
+          <t>25040.84433571342</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>2118083.0</t>
+          <t>2057561.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>-31.53</t>
+          <t>-31.62</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9732,12 +9732,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>34.62</t>
+          <t>34.68</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>3071</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9757,22 +9757,22 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="CX19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>11.0</t>
         </is>
       </c>
     </row>
@@ -9809,12 +9809,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>40.565</t>
+          <t>52.072</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9824,149 +9824,149 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>40.6</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>15.99</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2025-06-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2024-11-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2024-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>61.2</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>60.7</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>70.8</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>69.7</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>-33.11</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>-12.20</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024/11/05</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>70.7</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>2025/07/31</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>58.8</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>2024/11/19</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>69.4</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>2026/01/22</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
           <t>40.7</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>3.9</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>-0.66</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>22.82</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2025-06-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2024-11-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2024-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>61.2</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>60.7</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>70.8</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>69.7</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>-32.95</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>-12.20</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2024/11/05</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>70.7</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>2025/07/31</t>
-        </is>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>58.8</t>
-        </is>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>2024/11/19</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>69.4</t>
-        </is>
-      </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>2026/01/22</t>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>40.7</t>
-        </is>
-      </c>
       <c r="AI20" t="inlineStr">
         <is>
           <t>2025/12/11</t>
@@ -9984,17 +9984,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -10005,12 +10005,12 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -10020,51 +10020,51 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>-1.21</v>
+        <v>-0.98</v>
       </c>
       <c r="AV20" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-1.06</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>41.49</v>
+        <v>41.44</v>
       </c>
       <c r="BA20" t="n">
-        <v>42.33</v>
+        <v>42.27</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>43.29</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-5.01</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>-0.36</v>
+        <v>-0.39</v>
       </c>
       <c r="BE20" t="n">
-        <v>-0.34</v>
+        <v>-0.35</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
@@ -10073,7 +10073,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-135.57</t>
+          <t>-136.60</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -10083,43 +10083,43 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>7435306.067193676</t>
+          <t>7453881.860946746</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>1655115.0</t>
+          <t>2118083.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>2882296.2</v>
+        <v>2732836.8</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>2346796.6</t>
+          <t>2355995.8</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>2197559.12</v>
+        <v>2171316.48</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>535499</t>
+          <t>376841</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>86598.18192261527</t>
+          <t>83273.79138100205</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>113253.7976612188</t>
+          <t>64989.64340212941</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>1655115.0</t>
+          <t>2118083.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>-31.37</t>
+          <t>-31.53</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
@@ -10224,12 +10224,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>34.62</t>
+          <t>34.68</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>3071</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10249,22 +10249,22 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10284,14 +10284,14 @@
       </c>
       <c r="CX20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>11.0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -10301,12 +10301,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>115.01</t>
+          <t>40.565</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10326,17 +10326,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>22.82</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-32.62</t>
+          <t>-32.95</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -10426,7 +10426,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10476,17 +10476,17 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>7.70</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10497,12 +10497,12 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -10512,48 +10512,48 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>14.04</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>-1.35</v>
+        <v>-1.21</v>
       </c>
       <c r="AV21" t="n">
-        <v>-0.16</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>41.45999999999999</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>41.53</v>
+        <v>41.49</v>
       </c>
       <c r="BA21" t="n">
-        <v>42.38</v>
+        <v>42.33</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>-5.01</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>-0.32</v>
+        <v>-0.36</v>
       </c>
       <c r="BE21" t="n">
         <v>-0.34</v>
@@ -10565,7 +10565,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-135.12</t>
+          <t>-135.57</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10575,43 +10575,43 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>7435306.067193676</t>
+          <t>7453881.860946746</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>4721762.0</t>
+          <t>1655115.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>2997561.4</v>
+        <v>2882296.2</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>2477506.7</t>
+          <t>2346796.6</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>2270637.82</v>
+        <v>2197559.12</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>520054</t>
+          <t>535499</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>81751.70633377827</t>
+          <t>86598.18192261527</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>227761.5252577313</t>
+          <t>113253.7976612188</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>4721762.0</t>
+          <t>1655115.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10631,7 +10631,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>-31.03</t>
+          <t>-31.37</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10676,7 +10676,7 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>34.62</t>
+          <t>34.68</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>3071</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10741,22 +10741,22 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10776,7 +10776,7 @@
       </c>
       <c r="CX21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11.0</t>
         </is>
       </c>
     </row>
@@ -10793,12 +10793,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>37.287</t>
+          <t>115.01</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10818,17 +10818,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10893,7 +10893,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-32.04</t>
+          <t>-32.62</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -10918,7 +10918,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10968,17 +10968,17 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>7.70</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10989,63 +10989,63 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>14.04</t>
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>-0.63</v>
+        <v>-1.35</v>
       </c>
       <c r="AV22" t="n">
         <v>-0.16</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>41.51</t>
+          <t>41.45999999999999</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>41.58</v>
+        <v>41.53</v>
       </c>
       <c r="BA22" t="n">
-        <v>42.41</v>
+        <v>42.38</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>43.47</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>14.85</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>-0.29</v>
+        <v>-0.32</v>
       </c>
       <c r="BE22" t="n">
         <v>-0.34</v>
@@ -11057,7 +11057,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-135.52</t>
+          <t>-135.12</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -11067,43 +11067,43 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>7435306.067193676</t>
+          <t>7453881.860946746</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>1542732.0</t>
+          <t>4721762.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>2385302.4</v>
+        <v>2997561.4</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>2294484.4</t>
+          <t>2477506.7</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>2236735.98</v>
+        <v>2270637.82</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>90818</t>
+          <t>520054</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>55204.46652942317</t>
+          <t>81751.70633377827</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>54640.33163640229</t>
+          <t>227761.5252577313</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>1542732.0</t>
+          <t>4721762.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -11123,7 +11123,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>-30.44</t>
+          <t>-31.03</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>34.62</t>
+          <t>34.68</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>3071</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11233,22 +11233,22 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11268,7 +11268,7 @@
       </c>
       <c r="CX22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10.0</t>
         </is>
       </c>
     </row>
@@ -11285,12 +11285,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>86.561</t>
+          <t>37.287</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11310,17 +11310,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11385,7 +11385,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-31.55</t>
+          <t>-32.04</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11460,17 +11460,17 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11481,29 +11481,29 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>13.16</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>37.72</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>0.22</v>
+        <v>-0.63</v>
       </c>
       <c r="AV23" t="n">
-        <v>-0.33</v>
+        <v>-0.16</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
@@ -11512,35 +11512,35 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>41.45999999999999</t>
+          <t>41.51</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>41.6</v>
+        <v>41.58</v>
       </c>
       <c r="BA23" t="n">
-        <v>42.43</v>
+        <v>42.41</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>43.54</t>
+          <t>43.47</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>14.85</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>-0.28</v>
+        <v>-0.29</v>
       </c>
       <c r="BE23" t="n">
-        <v>-0.36</v>
+        <v>-0.34</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-136.84</t>
+          <t>-135.52</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11559,43 +11559,43 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>7435306.067193676</t>
+          <t>7453881.860946746</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>3626492.0</t>
+          <t>1542732.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>2427701.2</v>
+        <v>2385302.4</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>2371803.7</t>
+          <t>2294484.4</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>2236811.2</v>
+        <v>2236735.98</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>55897</t>
+          <t>90818</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>55307.03650997241</t>
+          <t>55204.46652942317</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>145983.2574760602</t>
+          <t>54640.33163640229</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>3626492.0</t>
+          <t>1542732.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11615,7 +11615,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>-29.93</t>
+          <t>-30.44</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11660,7 +11660,7 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>34.62</t>
+          <t>34.68</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>3071</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11725,22 +11725,22 @@
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>42.45</t>
+          <t>41.55</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>42.45</t>
+          <t>41.55</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11760,7 +11760,7 @@
       </c>
       <c r="CX23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9.0</t>
         </is>
       </c>
     </row>
@@ -11777,12 +11777,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>170.283</t>
+          <t>196.33</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>63.7</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>9.80</t>
+          <t>19.16</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -11952,17 +11952,17 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -11978,33 +11978,33 @@
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>31.57</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>0.54</v>
+        <v>-0.41</v>
       </c>
       <c r="AV24" t="n">
-        <v>-2.12</v>
+        <v>-1.77</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -12013,26 +12013,26 @@
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>64.73</v>
+        <v>64.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>65.37</v>
+        <v>65.28</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>66.91</t>
+          <t>66.79</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>-13.92</t>
+          <t>-11.64</t>
         </is>
       </c>
       <c r="BD24" t="n">
-        <v>-0.74</v>
+        <v>-0.75</v>
       </c>
       <c r="BE24" t="n">
-        <v>-0.65</v>
+        <v>-0.67</v>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-129.21</t>
+          <t>-130.09</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -12051,43 +12051,43 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>40035261.45463918</t>
+          <t>39991174.25</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>10912503.0</t>
+          <t>12405920.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>6082012.6</v>
+        <v>7565674.4</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>5539199.3</t>
+          <t>6349216.5</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>6314109.14</v>
+        <v>6294708.94</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>542813</t>
+          <t>1216457</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>-73849.03909094637</t>
+          <t>57194.83320573541</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>361830.4726555534</t>
+          <t>777936.1308374852</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>10912503.0</t>
+          <t>12405920.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -12107,7 +12107,7 @@
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
@@ -12152,7 +12152,7 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12177,7 +12177,7 @@
       </c>
       <c r="CI24" t="inlineStr">
         <is>
-          <t>31.38</t>
+          <t>31.08</t>
         </is>
       </c>
       <c r="CJ24" t="inlineStr">
@@ -12192,12 +12192,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>58.04</t>
+          <t>56.92</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>5462</t>
+          <t>5410</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12217,22 +12217,22 @@
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.1</t>
         </is>
       </c>
       <c r="CR24" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
-          <t>63.6</t>
+          <t>62.8</t>
         </is>
       </c>
       <c r="CT24" t="inlineStr">
         <is>
-          <t>63.7</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
@@ -12252,29 +12252,29 @@
       </c>
       <c r="CX24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>81.467</t>
+          <t>170.283</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>63.7</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -12294,17 +12294,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>9.80</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12319,32 +12319,32 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2025-08-04 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2025-08-20 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2025-07-25 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2025-07-28 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>33.05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -12354,12 +12354,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>32.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -12369,22 +12369,22 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025/02/21</t>
+          <t>2025/09/18</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -12394,52 +12394,52 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2025/08/28</t>
+          <t>2025/12/24</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>2025/04/08</t>
+          <t>2025/10/08</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>2025/12/10</t>
+          <t>2025/12/12</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>2025/12/08</t>
+          <t>2025/11/05</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>64.6</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>2025-08-20 00:00:00</t>
+          <t>2025-05-28 00:00:00</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -12465,286 +12465,1270 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
+          <t>58.33</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr">
+        <is>
+          <t>31.57</t>
+        </is>
+      </c>
+      <c r="AU25" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>-2.12</v>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>-0.99</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>-2.30</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>63.36</t>
+        </is>
+      </c>
+      <c r="AZ25" t="n">
+        <v>64.73</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>65.37</v>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>66.91</t>
+        </is>
+      </c>
+      <c r="BC25" t="inlineStr">
+        <is>
+          <t>-13.92</t>
+        </is>
+      </c>
+      <c r="BD25" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="BF25" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="BG25" t="inlineStr">
+        <is>
+          <t>-129.21</t>
+        </is>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="BI25" t="inlineStr">
+        <is>
+          <t>39991174.25</t>
+        </is>
+      </c>
+      <c r="BJ25" t="inlineStr">
+        <is>
+          <t>10912503.0</t>
+        </is>
+      </c>
+      <c r="BK25" t="n">
+        <v>6082012.6</v>
+      </c>
+      <c r="BL25" t="inlineStr">
+        <is>
+          <t>5539199.3</t>
+        </is>
+      </c>
+      <c r="BM25" t="n">
+        <v>6314109.14</v>
+      </c>
+      <c r="BN25" t="inlineStr">
+        <is>
+          <t>542813</t>
+        </is>
+      </c>
+      <c r="BO25" t="inlineStr">
+        <is>
+          <t>-73849.03909094637</t>
+        </is>
+      </c>
+      <c r="BP25" t="inlineStr">
+        <is>
+          <t>361830.4726555534</t>
+        </is>
+      </c>
+      <c r="BQ25" t="inlineStr">
+        <is>
+          <t>10912503.0</t>
+        </is>
+      </c>
+      <c r="BR25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS25" t="inlineStr">
+        <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="BT25" t="inlineStr">
+        <is>
+          <t>2025/12/19</t>
+        </is>
+      </c>
+      <c r="BU25" t="inlineStr">
+        <is>
+          <t>-0.47</t>
+        </is>
+      </c>
+      <c r="BV25" t="inlineStr">
+        <is>
+          <t>寶齡富錦</t>
+        </is>
+      </c>
+      <c r="BW25" t="inlineStr">
+        <is>
+          <t>寶齡富錦</t>
+        </is>
+      </c>
+      <c r="BX25" t="inlineStr">
+        <is>
+          <t>生技醫療業</t>
+        </is>
+      </c>
+      <c r="BY25" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BZ25" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="CA25" t="inlineStr">
+        <is>
+          <t>-22.55378299170716</t>
+        </is>
+      </c>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t>14.88387829883942</t>
+        </is>
+      </c>
+      <c r="CC25" t="inlineStr">
+        <is>
+          <t>1.662704561635163</t>
+        </is>
+      </c>
+      <c r="CD25" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE25" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CF25" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="CG25" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="CH25" t="inlineStr">
+        <is>
+          <t>6.20</t>
+        </is>
+      </c>
+      <c r="CI25" t="inlineStr">
+        <is>
+          <t>31.08</t>
+        </is>
+      </c>
+      <c r="CJ25" t="inlineStr">
+        <is>
+          <t>56.45%</t>
+        </is>
+      </c>
+      <c r="CK25" t="inlineStr">
+        <is>
+          <t>18.71%</t>
+        </is>
+      </c>
+      <c r="CL25" t="inlineStr">
+        <is>
+          <t>56.92</t>
+        </is>
+      </c>
+      <c r="CM25" t="inlineStr">
+        <is>
+          <t>5410</t>
+        </is>
+      </c>
+      <c r="CN25" t="inlineStr">
+        <is>
+          <t>藥品38.92%、權利金收入20.27%、食品17.41%、化工8.69%、原料藥(API)8.12%、檢驗試劑5.07%、里程金1.10%、醫美醫材0.43% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO25" t="inlineStr">
+        <is>
+          <t>寶齡富錦-生技醫療業-上市</t>
+        </is>
+      </c>
+      <c r="CP25" t="inlineStr">
+        <is>
+          <t>生技醫療業右下上市</t>
+        </is>
+      </c>
+      <c r="CQ25" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="CR25" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="CS25" t="inlineStr">
+        <is>
+          <t>63.6</t>
+        </is>
+      </c>
+      <c r="CT25" t="inlineStr">
+        <is>
+          <t>63.7</t>
+        </is>
+      </c>
+      <c r="CU25" t="inlineStr">
+        <is>
+          <t>22.18</t>
+        </is>
+      </c>
+      <c r="CV25" t="inlineStr">
+        <is>
+          <t>** 石化及塑橡膠 - 化妝品** 製藥 - 中、西藥製劑、藥品代理銷售及通路** 食品生技 - 加工製成品、保健食品代理銷售及通路** 醫療器材 - 醫療耗材、生物檢測</t>
+        </is>
+      </c>
+      <c r="CW25" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CX25" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1737</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>52.658</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>31.5</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>4.46</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2025-08-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2025-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2025-07-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2025-07-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>33.05</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>32.25</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>32.9</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>32.75</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>-2.33</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025/02/21</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>32.7</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>2025/08/28</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>32.2</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>2025/04/08</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>30.65</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>31.6</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>31.6</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>2025-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>5.18</t>
+        </is>
+      </c>
+      <c r="AN26" t="inlineStr">
+        <is>
+          <t>-0.32</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr"/>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
           <t>14.29</t>
         </is>
       </c>
-      <c r="AT25" t="inlineStr">
+      <c r="AT26" t="inlineStr">
+        <is>
+          <t>33.33</t>
+        </is>
+      </c>
+      <c r="AU26" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>-0.39</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>-0.49</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>31.6</t>
+        </is>
+      </c>
+      <c r="AZ26" t="n">
+        <v>31.59</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>31.71</v>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>31.87</t>
+        </is>
+      </c>
+      <c r="BC26" t="inlineStr">
+        <is>
+          <t>8.23</t>
+        </is>
+      </c>
+      <c r="BD26" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="BF26" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="BG26" t="inlineStr">
+        <is>
+          <t>-113.78</t>
+        </is>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>2025/12/19</t>
+        </is>
+      </c>
+      <c r="BI26" t="inlineStr">
+        <is>
+          <t>11302230.99382716</t>
+        </is>
+      </c>
+      <c r="BJ26" t="inlineStr">
+        <is>
+          <t>1660091.0</t>
+        </is>
+      </c>
+      <c r="BK26" t="n">
+        <v>3220987.4</v>
+      </c>
+      <c r="BL26" t="inlineStr">
+        <is>
+          <t>3083421.0</t>
+        </is>
+      </c>
+      <c r="BM26" t="n">
+        <v>3297756.66</v>
+      </c>
+      <c r="BN26" t="inlineStr">
+        <is>
+          <t>137566</t>
+        </is>
+      </c>
+      <c r="BO26" t="inlineStr">
+        <is>
+          <t>-16709.90572409765</t>
+        </is>
+      </c>
+      <c r="BP26" t="inlineStr">
+        <is>
+          <t>-87417.93593248213</t>
+        </is>
+      </c>
+      <c r="BQ26" t="inlineStr">
+        <is>
+          <t>1660091.0</t>
+        </is>
+      </c>
+      <c r="BR26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS26" t="inlineStr">
+        <is>
+          <t>32.7</t>
+        </is>
+      </c>
+      <c r="BT26" t="inlineStr">
+        <is>
+          <t>2025/05/19</t>
+        </is>
+      </c>
+      <c r="BU26" t="inlineStr">
+        <is>
+          <t>-3.67</t>
+        </is>
+      </c>
+      <c r="BV26" t="inlineStr">
+        <is>
+          <t>臺鹽</t>
+        </is>
+      </c>
+      <c r="BW26" t="inlineStr">
+        <is>
+          <t>臺鹽</t>
+        </is>
+      </c>
+      <c r="BX26" t="inlineStr">
+        <is>
+          <t>食品工業</t>
+        </is>
+      </c>
+      <c r="BY26" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BZ26" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="CA26" t="inlineStr">
+        <is>
+          <t>11.30964198266164</t>
+        </is>
+      </c>
+      <c r="CB26" t="inlineStr">
+        <is>
+          <t>7.950770160072485</t>
+        </is>
+      </c>
+      <c r="CC26" t="inlineStr">
+        <is>
+          <t>2.099499961706554</t>
+        </is>
+      </c>
+      <c r="CD26" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE26" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CF26" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="CG26" t="inlineStr">
+        <is>
+          <t>4.13</t>
+        </is>
+      </c>
+      <c r="CH26" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
+      </c>
+      <c r="CI26" t="inlineStr">
+        <is>
+          <t>18.86</t>
+        </is>
+      </c>
+      <c r="CJ26" t="inlineStr">
+        <is>
+          <t>39.76%</t>
+        </is>
+      </c>
+      <c r="CK26" t="inlineStr">
+        <is>
+          <t>11.78%</t>
+        </is>
+      </c>
+      <c r="CL26" t="inlineStr">
+        <is>
+          <t>25.51</t>
+        </is>
+      </c>
+      <c r="CM26" t="inlineStr">
+        <is>
+          <t>6300</t>
+        </is>
+      </c>
+      <c r="CN26" t="inlineStr">
+        <is>
+          <t>鹽46.50%、包裝飲用水34.02%、清潔用品5.33%、保健食品5.08%、美容保養品4.12%、工程及勞務2.55%、其他2.39% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO26" t="inlineStr">
+        <is>
+          <t>臺鹽-食品工業-上市</t>
+        </is>
+      </c>
+      <c r="CP26" t="inlineStr">
+        <is>
+          <t>食品工業右下上市</t>
+        </is>
+      </c>
+      <c r="CQ26" t="inlineStr">
+        <is>
+          <t>31.5</t>
+        </is>
+      </c>
+      <c r="CR26" t="inlineStr">
+        <is>
+          <t>31.6</t>
+        </is>
+      </c>
+      <c r="CS26" t="inlineStr">
+        <is>
+          <t>31.5</t>
+        </is>
+      </c>
+      <c r="CT26" t="inlineStr">
+        <is>
+          <t>31.5</t>
+        </is>
+      </c>
+      <c r="CU26" t="inlineStr">
+        <is>
+          <t>33.23</t>
+        </is>
+      </c>
+      <c r="CV26" t="inlineStr">
+        <is>
+          <t>** 食品 - 原物料、營養食品** 石化及塑橡膠 - 化妝品</t>
+        </is>
+      </c>
+      <c r="CW26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CX26" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1737</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>-0.32</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>81.467</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>31.5</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>4.84</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2025-08-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2025-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2025-07-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2025-07-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>33.05</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>32.25</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>32.9</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>32.75</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>-2.33</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025/02/21</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>32.7</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>2025/08/28</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>32.2</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>2025/04/08</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>30.65</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>31.6</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>31.6</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>2025-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>8.01</t>
+        </is>
+      </c>
+      <c r="AN27" t="inlineStr">
+        <is>
+          <t>-0.16</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr"/>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>14.29</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr">
         <is>
           <t>42.86</t>
         </is>
       </c>
-      <c r="AU25" t="n">
+      <c r="AU27" t="n">
         <v>-0.44</v>
       </c>
-      <c r="AV25" t="n">
+      <c r="AV27" t="n">
         <v>0.14</v>
       </c>
-      <c r="AW25" t="inlineStr">
+      <c r="AW27" t="inlineStr">
         <is>
           <t>-0.4</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
+      <c r="AX27" t="inlineStr">
         <is>
           <t>-0.49</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr">
+      <c r="AY27" t="inlineStr">
         <is>
           <t>31.64</t>
         </is>
       </c>
-      <c r="AZ25" t="n">
+      <c r="AZ27" t="n">
         <v>31.6</v>
       </c>
-      <c r="BA25" t="n">
+      <c r="BA27" t="n">
         <v>31.72</v>
       </c>
-      <c r="BB25" t="inlineStr">
+      <c r="BB27" t="inlineStr">
         <is>
           <t>31.88</t>
         </is>
       </c>
-      <c r="BC25" t="inlineStr">
+      <c r="BC27" t="inlineStr">
         <is>
           <t>25.55</t>
         </is>
       </c>
-      <c r="BD25" t="n">
+      <c r="BD27" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BE25" t="n">
+      <c r="BE27" t="n">
         <v>-0.04</v>
       </c>
-      <c r="BF25" t="inlineStr">
+      <c r="BF27" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="BG25" t="inlineStr">
+      <c r="BG27" t="inlineStr">
         <is>
           <t>-114.07</t>
         </is>
       </c>
-      <c r="BH25" t="inlineStr">
+      <c r="BH27" t="inlineStr">
         <is>
           <t>2025/12/19</t>
         </is>
       </c>
-      <c r="BI25" t="inlineStr">
-        <is>
-          <t>11320400.26082474</t>
-        </is>
-      </c>
-      <c r="BJ25" t="inlineStr">
+      <c r="BI27" t="inlineStr">
+        <is>
+          <t>11302230.99382716</t>
+        </is>
+      </c>
+      <c r="BJ27" t="inlineStr">
         <is>
           <t>2568418.0</t>
         </is>
       </c>
-      <c r="BK25" t="n">
+      <c r="BK27" t="n">
         <v>3289054.2</v>
       </c>
-      <c r="BL25" t="inlineStr">
+      <c r="BL27" t="inlineStr">
         <is>
           <t>3137217.9</t>
         </is>
       </c>
-      <c r="BM25" t="n">
+      <c r="BM27" t="n">
         <v>3324051.1</v>
       </c>
-      <c r="BN25" t="inlineStr">
+      <c r="BN27" t="inlineStr">
         <is>
           <t>151836</t>
         </is>
       </c>
-      <c r="BO25" t="inlineStr">
+      <c r="BO27" t="inlineStr">
         <is>
           <t>-3853.900231664111</t>
         </is>
       </c>
-      <c r="BP25" t="inlineStr">
+      <c r="BP27" t="inlineStr">
         <is>
           <t>32790.85744653689</t>
         </is>
       </c>
-      <c r="BQ25" t="inlineStr">
+      <c r="BQ27" t="inlineStr">
         <is>
           <t>2568418.0</t>
         </is>
       </c>
-      <c r="BR25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS25" t="inlineStr">
+      <c r="BR27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS27" t="inlineStr">
         <is>
           <t>32.7</t>
         </is>
       </c>
-      <c r="BT25" t="inlineStr">
+      <c r="BT27" t="inlineStr">
         <is>
           <t>2025/05/19</t>
         </is>
       </c>
-      <c r="BU25" t="inlineStr">
+      <c r="BU27" t="inlineStr">
         <is>
           <t>-3.67</t>
         </is>
       </c>
-      <c r="BV25" t="inlineStr">
+      <c r="BV27" t="inlineStr">
         <is>
           <t>臺鹽</t>
         </is>
       </c>
-      <c r="BW25" t="inlineStr">
+      <c r="BW27" t="inlineStr">
         <is>
           <t>臺鹽</t>
         </is>
       </c>
-      <c r="BX25" t="inlineStr">
+      <c r="BX27" t="inlineStr">
         <is>
           <t>食品工業</t>
         </is>
       </c>
-      <c r="BY25" t="inlineStr">
+      <c r="BY27" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BZ25" t="inlineStr">
+      <c r="BZ27" t="inlineStr">
         <is>
           <t>0.28</t>
         </is>
       </c>
-      <c r="CA25" t="inlineStr">
+      <c r="CA27" t="inlineStr">
         <is>
           <t>11.30964198266164</t>
         </is>
       </c>
-      <c r="CB25" t="inlineStr">
+      <c r="CB27" t="inlineStr">
         <is>
           <t>7.950770160072485</t>
         </is>
       </c>
-      <c r="CC25" t="inlineStr">
+      <c r="CC27" t="inlineStr">
         <is>
           <t>2.099499961706554</t>
         </is>
       </c>
-      <c r="CD25" t="inlineStr">
+      <c r="CD27" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="CE25" t="inlineStr">
+      <c r="CE27" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CF25" t="inlineStr">
+      <c r="CF27" t="inlineStr">
         <is>
           <t>0.95</t>
         </is>
       </c>
-      <c r="CG25" t="inlineStr">
+      <c r="CG27" t="inlineStr">
         <is>
           <t>4.13</t>
         </is>
       </c>
-      <c r="CH25" t="inlineStr">
+      <c r="CH27" t="inlineStr">
         <is>
           <t>4.07</t>
         </is>
       </c>
-      <c r="CI25" t="inlineStr">
+      <c r="CI27" t="inlineStr">
         <is>
           <t>18.86</t>
         </is>
       </c>
-      <c r="CJ25" t="inlineStr">
+      <c r="CJ27" t="inlineStr">
         <is>
           <t>39.76%</t>
         </is>
       </c>
-      <c r="CK25" t="inlineStr">
+      <c r="CK27" t="inlineStr">
         <is>
           <t>11.78%</t>
         </is>
       </c>
-      <c r="CL25" t="inlineStr">
-        <is>
-          <t>25.33</t>
-        </is>
-      </c>
-      <c r="CM25" t="inlineStr">
+      <c r="CL27" t="inlineStr">
+        <is>
+          <t>25.51</t>
+        </is>
+      </c>
+      <c r="CM27" t="inlineStr">
         <is>
           <t>6300</t>
         </is>
       </c>
-      <c r="CN25" t="inlineStr">
+      <c r="CN27" t="inlineStr">
         <is>
           <t>鹽46.50%、包裝飲用水34.02%、清潔用品5.33%、保健食品5.08%、美容保養品4.12%、工程及勞務2.55%、其他2.39% (2024年)</t>
         </is>
       </c>
-      <c r="CO25" t="inlineStr">
+      <c r="CO27" t="inlineStr">
         <is>
           <t>臺鹽-食品工業-上市</t>
         </is>
       </c>
-      <c r="CP25" t="inlineStr">
+      <c r="CP27" t="inlineStr">
         <is>
           <t>食品工業右下上市</t>
         </is>
       </c>
-      <c r="CQ25" t="inlineStr">
+      <c r="CQ27" t="inlineStr">
         <is>
           <t>31.6</t>
         </is>
       </c>
-      <c r="CR25" t="inlineStr">
+      <c r="CR27" t="inlineStr">
         <is>
           <t>31.6</t>
         </is>
       </c>
-      <c r="CS25" t="inlineStr">
+      <c r="CS27" t="inlineStr">
         <is>
           <t>31.45</t>
         </is>
       </c>
-      <c r="CT25" t="inlineStr">
+      <c r="CT27" t="inlineStr">
         <is>
           <t>31.5</t>
         </is>
       </c>
-      <c r="CU25" t="inlineStr">
+      <c r="CU27" t="inlineStr">
         <is>
           <t>33.23</t>
         </is>
       </c>
-      <c r="CV25" t="inlineStr">
+      <c r="CV27" t="inlineStr">
         <is>
           <t>** 食品 - 原物料、營養食品** 石化及塑橡膠 - 化妝品</t>
         </is>
       </c>
-      <c r="CW25" t="inlineStr">
+      <c r="CW27" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="CX25" t="inlineStr">
-        <is>
-          <t>7</t>
+      <c r="CX27" t="inlineStr">
+        <is>
+          <t>7.0</t>
         </is>
       </c>
     </row>

--- a/Result/checksun_type/化妝品.xlsx
+++ b/Result/checksun_type/化妝品.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CX27"/>
+  <dimension ref="A1:CY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -939,6 +939,11 @@
           <t>盤整震盪_前15日次數</t>
         </is>
       </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>多頭排列_前5日次數</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -978,12 +983,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -998,7 +1003,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1149,12 +1154,12 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>710</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1217,7 +1222,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-80.69</t>
+          <t>-80.63</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1227,7 +1232,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>69013672.0147929</t>
+          <t>32665730.04</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1253,12 +1258,12 @@
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>9816999.517420726</t>
+          <t>9816999.517420098</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>11594304.76359032</t>
+          <t>11594304.76359017</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1368,12 +1373,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3331</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,7 +1393,7 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>其他右下上市</t>
+          <t>其他平上市</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
@@ -1428,7 +1433,12 @@
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1470,12 +1480,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1490,7 +1500,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1641,12 +1651,12 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>710</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1709,7 +1719,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-83.08</t>
+          <t>-83.03</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1719,7 +1729,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>69013672.0147929</t>
+          <t>32665730.04</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1745,12 +1755,12 @@
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>9493853.109026255</t>
+          <t>9493853.109025538</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>17859478.60877223</t>
+          <t>17859478.60877207</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1860,12 +1870,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3331</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1880,7 +1890,7 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>其他右下上市</t>
+          <t>其他平上市</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
@@ -1920,7 +1930,12 @@
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="CY3" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1962,12 +1977,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1982,7 +1997,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2133,12 +2148,12 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>710</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -2201,7 +2216,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-86.85</t>
+          <t>-86.80</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2211,7 +2226,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>69013672.0147929</t>
+          <t>32665730.04</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -2237,12 +2252,12 @@
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>7972830.290890622</t>
+          <t>7972830.290889805</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>20307128.75871883</t>
+          <t>20307128.75871864</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2352,12 +2367,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3331</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2372,7 +2387,7 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>其他右下上市</t>
+          <t>其他平上市</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
@@ -2412,7 +2427,12 @@
       </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="CY4" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2454,12 +2474,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2474,7 +2494,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2625,12 +2645,12 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>710</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2693,7 +2713,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-91.55</t>
+          <t>-91.52</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2703,7 +2723,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>69013672.0147929</t>
+          <t>32665730.04</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2729,12 +2749,12 @@
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>5730230.569467312</t>
+          <t>5730230.56946638</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>25668916.73154542</t>
+          <t>25668916.73154521</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2844,12 +2864,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3331</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2864,7 +2884,7 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>其他右下上市</t>
+          <t>其他平上市</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
@@ -2904,7 +2924,12 @@
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="CY5" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2946,12 +2971,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-14.58</t>
+          <t>-15.25</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2966,7 +2991,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -3117,12 +3142,12 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>710</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -3195,7 +3220,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>69013672.0147929</t>
+          <t>32665730.04</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -3221,12 +3246,12 @@
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>2105014.903634928</t>
+          <t>2105014.903633866</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>8653579.166599646</t>
+          <t>8653579.166599419</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3336,12 +3361,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3331</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3356,7 +3381,7 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>其他右下上市</t>
+          <t>其他平上市</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
@@ -3396,7 +3421,12 @@
       </c>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="CY6" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3438,12 +3468,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -3458,7 +3488,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3609,12 +3639,12 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>710</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3677,7 +3707,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-105.92</t>
+          <t>-105.94</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3687,7 +3717,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>69013672.0147929</t>
+          <t>32665730.04</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -3713,12 +3743,12 @@
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>914366.8558231613</t>
+          <t>914366.8558219471</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>4009574.032155704</t>
+          <t>4009574.032155443</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3828,12 +3858,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3331</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3848,7 +3878,7 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>其他右下上市</t>
+          <t>其他平上市</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
@@ -3888,7 +3918,12 @@
       </c>
       <c r="CX7" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="CY7" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3930,12 +3965,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -3950,7 +3985,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -4101,12 +4136,12 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>710</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -4169,7 +4204,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-108.19</t>
+          <t>-108.22</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4179,7 +4214,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>69013672.0147929</t>
+          <t>32665730.04</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -4205,12 +4240,12 @@
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>351601.9146717899</t>
+          <t>351601.9146704023</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>565374.8389445115</t>
+          <t>565374.8389442144</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4320,12 +4355,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3331</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4340,7 +4375,7 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>其他右下上市</t>
+          <t>其他平上市</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
@@ -4380,7 +4415,12 @@
       </c>
       <c r="CX8" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="CY8" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4422,12 +4462,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -4442,7 +4482,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4593,12 +4633,12 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>710</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4661,7 +4701,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-107.35</t>
+          <t>-107.38</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4671,7 +4711,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>69013672.0147929</t>
+          <t>32665730.04</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -4697,12 +4737,12 @@
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>312734.1102585678</t>
+          <t>312734.1102569819</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-16139.71703378018</t>
+          <t>-16139.71703412011</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4812,12 +4852,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3331</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4832,7 +4872,7 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>其他右下上市</t>
+          <t>其他平上市</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
@@ -4872,7 +4912,12 @@
       </c>
       <c r="CX9" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="CY9" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4914,12 +4959,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -4934,7 +4979,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -5085,12 +5130,12 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>710</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -5153,7 +5198,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-106.31</t>
+          <t>-106.33</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5163,7 +5208,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>69013672.0147929</t>
+          <t>32665730.04</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -5189,12 +5234,12 @@
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>372529.3515844492</t>
+          <t>372529.3515826368</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>131584.8357484369</t>
+          <t>131584.8357480485</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5269,7 +5314,7 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -5304,12 +5349,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3331</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5324,7 +5369,7 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>其他右下上市</t>
+          <t>其他平上市</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
@@ -5364,7 +5409,12 @@
       </c>
       <c r="CX10" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="CY10" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -5406,12 +5456,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -5426,7 +5476,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5577,12 +5627,12 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>710</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5645,7 +5695,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-105.50</t>
+          <t>-105.51</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5655,7 +5705,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>69013672.0147929</t>
+          <t>32665730.04</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -5681,12 +5731,12 @@
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>416337.4453728151</t>
+          <t>416337.4453707437</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>318760.4170177318</t>
+          <t>318760.4170172876</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5796,12 +5846,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3331</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5816,7 +5866,7 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>其他右下上市</t>
+          <t>其他平上市</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
@@ -5856,29 +5906,34 @@
       </c>
       <c r="CX11" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="CY11" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>9919</t>
+          <t>6504</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>388.233</t>
+          <t>267.325</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5888,7 +5943,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>16.25</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5898,17 +5953,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-9.80</t>
+          <t>48.46</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5918,7 +5973,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5983,12 +6038,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025/10/17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -5998,67 +6053,67 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/07/31</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2025/07/07</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2026/01/20</t>
+          <t>2026/01/22</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>16.25</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2025/12/26</t>
+          <t>2025/12/11</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2026-01-29 00:00:00</t>
+          <t>2026-01-27 00:00:00</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>17.91</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6069,75 +6124,75 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>90</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>-1.69</v>
+        <v>-3.93</v>
       </c>
       <c r="AV12" t="n">
-        <v>-0.06</v>
+        <v>4.36</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>16.53</t>
+          <t>44.03</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>16.54</v>
+        <v>42.19</v>
       </c>
       <c r="BA12" t="n">
-        <v>16.64</v>
+        <v>42.38</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>43.18</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-20.44</t>
+          <t>76.88</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>-0.05</v>
+        <v>0.31</v>
       </c>
       <c r="BE12" t="n">
-        <v>-0.04</v>
+        <v>0.18</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-104.99</t>
+          <t>-81.76</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6147,43 +6202,43 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>69013672.0147929</t>
+          <t>6843513.258</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>6327582.0</t>
+          <t>11235489.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>6491295.8</v>
+        <v>26211444.6</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>7196752.8</t>
+          <t>17655876.5</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>5141183.88</v>
+        <v>5273864.44</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-705457</t>
+          <t>8555568</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>434078.7232555575</t>
+          <t>2719001.516642316</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>493371.0182232345</t>
+          <t>2674641.352217499</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>6327582.0</t>
+          <t>11235489.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6193,27 +6248,27 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>59.3</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2026/01/29</t>
+          <t>2025/05/26</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>-9.72</t>
+          <t>-28.67</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>康那香</t>
+          <t>南六</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
         <is>
-          <t>康那香</t>
+          <t>南六</t>
         </is>
       </c>
       <c r="BX12" t="inlineStr">
@@ -6228,47 +6283,47 @@
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
         <is>
-          <t>-2.134193013894768</t>
+          <t>-3.675038602250755</t>
         </is>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>-26.44797574412215</t>
+          <t>-14.32073522315297</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>-8.521537956848594</t>
+          <t>-1.501881912730951</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>22.20</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -6278,32 +6333,32 @@
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>12.86%</t>
         </is>
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>-22.56%</t>
+          <t>2.52%</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
-          <t>衛生棉54.52%、濕巾21.35%、紙尿褲13.15%、不織布及其他10.98% (2024年)</t>
+          <t>PP不織布30.93%、生技產品28.88%、水針布27.86%、水針後處理12.33% (2024年)</t>
         </is>
       </c>
       <c r="CO12" t="inlineStr">
         <is>
-          <t>康那香-其他-上市</t>
+          <t>南六-其他-上市</t>
         </is>
       </c>
       <c r="CP12" t="inlineStr">
@@ -6313,32 +6368,32 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>16.25</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>16.25</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>16.25</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
         <is>
-          <t>11.58</t>
+          <t>44.62</t>
         </is>
       </c>
       <c r="CV12" t="inlineStr">
         <is>
-          <t>** 石化及塑橡膠 - 清潔用品、化妝品** 紡織 - 成衣及其它家居紡織類品** 其他 - 其他** 醫療器材 - 衛生用品、醫療耗材</t>
+          <t>** 石化及塑橡膠 - 清潔用品、化妝品** 紡織 - 成衣及其它家居紡織類品** 醫療器材 - 衛生用品、醫療耗材</t>
         </is>
       </c>
       <c r="CW12" t="inlineStr">
@@ -6348,7 +6403,12 @@
       </c>
       <c r="CX12" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="CY12" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -6365,12 +6425,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>267.325</t>
+          <t>226.35</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6380,7 +6440,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6390,17 +6450,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>48.46</t>
+          <t>85.50</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6410,37 +6470,37 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2025-06-27 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-07-07 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2024-11-07 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2024-11-13 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -6450,12 +6510,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -6465,22 +6525,22 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-30.31</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024/11/05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -6490,7 +6550,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6505,12 +6565,12 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2024/11/19</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>69.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -6540,17 +6600,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>17.91</t>
+          <t>15.16</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6566,61 +6626,61 @@
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>90</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>-3.93</v>
+        <v>-4.81</v>
       </c>
       <c r="AV13" t="n">
-        <v>4.36</v>
+        <v>5.5</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>44.03</t>
+          <t>44.49</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>42.19</v>
+        <v>42.17</v>
       </c>
       <c r="BA13" t="n">
-        <v>42.38</v>
+        <v>42.39</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>43.18</t>
+          <t>43.22</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>76.88</t>
+          <t>167.39</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>0.31</v>
+        <v>0.38</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
@@ -6629,7 +6689,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-81.74</t>
+          <t>-85.27</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6639,43 +6699,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>7453881.860946746</t>
+          <t>6843513.258</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>11235489.0</t>
+          <t>9926503.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>26211444.6</v>
+        <v>30954151</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>17655876.5</t>
+          <t>16686600.8</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>5273864.44</v>
+        <v>5067898.96</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>8555568</t>
+          <t>14267550</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>2719001.516642336</t>
+          <t>2727067.001083192</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>2674641.352217507</t>
+          <t>3706873.146931387</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>11235489.0</t>
+          <t>9926503.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6695,7 +6755,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>-28.67</t>
+          <t>-28.58</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6740,12 +6800,12 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
@@ -6755,7 +6815,7 @@
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6780,12 +6840,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6805,22 +6865,22 @@
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6840,7 +6900,12 @@
       </c>
       <c r="CX13" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="CY13" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -6857,12 +6922,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>226.35</t>
+          <t>197.457</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6872,7 +6937,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6882,17 +6947,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>85.50</t>
+          <t>82.98</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6902,37 +6967,37 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2025-06-27 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2025-07-07 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2024-11-07 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2024-11-13 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -6942,12 +7007,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -6957,22 +7022,22 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-30.23</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024/11/05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -6982,7 +7047,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6997,12 +7062,12 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2024/11/19</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>69.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -7032,17 +7097,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>13.23</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -7058,61 +7123,61 @@
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>90</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>19.41</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>54.31</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>-4.81</v>
+        <v>-4.37</v>
       </c>
       <c r="AV14" t="n">
-        <v>5.5</v>
+        <v>4.72</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>44.49</t>
+          <t>44.13</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>42.17</v>
+        <v>42.14</v>
       </c>
       <c r="BA14" t="n">
-        <v>42.39</v>
+        <v>42.4</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>43.22</t>
+          <t>43.26</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>167.39</t>
+          <t>453.26</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>0.38</v>
+        <v>0.46</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7121,7 +7186,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-85.25</t>
+          <t>-91.43</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7131,43 +7196,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>7453881.860946746</t>
+          <t>6843513.258</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>9926503.0</t>
+          <t>8413534.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>30954151</v>
+        <v>29380362.6</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>16686600.8</t>
+          <t>16056599.7</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>5067898.96</v>
+        <v>4904141.1</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>14267550</t>
+          <t>13323762</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>2727067.001083214</t>
+          <t>2548920.429110793</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>3706873.146931395</t>
+          <t>5189350.169846535</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>9926503.0</t>
+          <t>8413534.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7187,7 +7252,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>-28.58</t>
+          <t>-28.84</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7247,7 +7312,7 @@
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -7272,12 +7337,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7297,22 +7362,22 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>44.15</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>44.15</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7332,7 +7397,12 @@
       </c>
       <c r="CX14" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="CY14" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -7349,12 +7419,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>197.457</t>
+          <t>1195.571</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7364,7 +7434,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7374,17 +7444,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>82.98</t>
+          <t>81.41</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7394,37 +7464,37 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2025-06-27 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2025-07-07 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2024-11-07 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2024-11-13 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -7434,12 +7504,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -7449,22 +7519,22 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-30.48</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024/11/05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -7474,7 +7544,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7489,12 +7559,12 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2024/11/19</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>69.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -7524,17 +7594,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>13.23</t>
+          <t>80.08</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>-19.10</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7550,61 +7620,61 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>90</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>19.41</t>
+          <t>43.53</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>54.31</t>
+          <t>81.18</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>-4.37</v>
+        <v>1</v>
       </c>
       <c r="AV15" t="n">
-        <v>4.72</v>
+        <v>4.09</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>44.13</t>
+          <t>43.81</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>42.14</v>
+        <v>42.09</v>
       </c>
       <c r="BA15" t="n">
         <v>42.4</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>43.26</t>
+          <t>43.29</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>453.26</t>
+          <t>5229.05</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>0.46</v>
+        <v>0.57</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.08</v>
+        <v>-0.01</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7613,7 +7683,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-91.42</t>
+          <t>-101.14</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7623,43 +7693,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>7453881.860946746</t>
+          <t>6843513.258</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>8413534.0</t>
+          <t>56593114.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>29380362.6</v>
+        <v>28121272.4</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>16056599.7</t>
+          <t>15501784.3</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>4904141.1</v>
+        <v>4746863</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>13323762</t>
+          <t>12619488</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>2548920.429110818</t>
+          <t>2068842.294431568</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>5189350.169846542</t>
+          <t>7283944.375087943</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>8413534.0</t>
+          <t>56593114.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7679,7 +7749,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>-28.84</t>
+          <t>-25.38</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7724,22 +7794,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -7764,12 +7834,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7789,22 +7859,22 @@
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="CR15" t="inlineStr">
+        <is>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="CS15" t="inlineStr">
+        <is>
           <t>44.15</t>
         </is>
       </c>
-      <c r="CR15" t="inlineStr">
-        <is>
-          <t>44.15</t>
-        </is>
-      </c>
-      <c r="CS15" t="inlineStr">
-        <is>
-          <t>42.15</t>
-        </is>
-      </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7824,7 +7894,12 @@
       </c>
       <c r="CX15" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="CY15" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -7841,12 +7916,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1195.571</t>
+          <t>924.579</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7856,7 +7931,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7866,17 +7941,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-16.79</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>81.41</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7886,37 +7961,37 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2025-06-27 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2025-07-07 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2024-11-07 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2024-11-13 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -7926,12 +8001,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -7941,22 +8016,22 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-27.10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024/11/05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -7966,7 +8041,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7981,12 +8056,12 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2024/11/19</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>69.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -8016,17 +8091,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>80.08</t>
+          <t>61.93</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>-19.10</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -8042,61 +8117,61 @@
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>90</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>43.53</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>81.18</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>1</v>
+        <v>13.81</v>
       </c>
       <c r="AV16" t="n">
-        <v>4.09</v>
+        <v>2.74</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>43.81</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>42.09</v>
+        <v>41.95</v>
       </c>
       <c r="BA16" t="n">
-        <v>42.4</v>
+        <v>42.35</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>43.29</t>
+          <t>43.31</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>5229.05</t>
+          <t>413.12</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>0.57</v>
+        <v>0.49</v>
       </c>
       <c r="BE16" t="n">
-        <v>-0.01</v>
+        <v>-0.16</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -8105,7 +8180,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-101.14</t>
+          <t>-116.05</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8115,43 +8190,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>7453881.860946746</t>
+          <t>6843513.258</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>56593114.0</t>
+          <t>44888583.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>28121272.4</v>
+        <v>17133672.6</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>15501784.3</t>
+          <t>10065617.0</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>4746863</v>
+        <v>3634806.6</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>12619488</t>
+          <t>7068055</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>2068842.294431595</t>
+          <t>1120641.916130409</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>7283944.37508795</t>
+          <t>4853983.083465384</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>56593114.0</t>
+          <t>44888583.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8171,7 +8246,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>-25.38</t>
+          <t>-17.28</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8216,22 +8291,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -8256,12 +8331,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8281,22 +8356,22 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>44.15</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8316,14 +8391,19 @@
       </c>
       <c r="CX16" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="CY16" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -8333,12 +8413,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>924.579</t>
+          <t>789.819</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8348,7 +8428,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8358,17 +8438,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-15.96</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>58.46</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8378,37 +8458,37 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2025-06-27 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2025-07-07 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2024-11-07 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2024-11-13 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -8418,12 +8498,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -8433,22 +8513,22 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-19.19</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024/11/05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -8458,7 +8538,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8473,12 +8553,12 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2024/11/19</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>69.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -8508,17 +8588,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>61.93</t>
+          <t>52.90</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>7.21</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8534,7 +8614,7 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>90</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -8544,51 +8624,51 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>13.81</v>
+        <v>7.55</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.74</v>
+        <v>-0.22</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>41.47000000000001</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>41.95</v>
+        <v>41.56</v>
       </c>
       <c r="BA17" t="n">
-        <v>42.35</v>
+        <v>42.22</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>43.31</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>413.12</t>
+          <t>64.79</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>0.49</v>
+        <v>-0.11</v>
       </c>
       <c r="BE17" t="n">
-        <v>-0.16</v>
+        <v>-0.32</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8597,7 +8677,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-116.07</t>
+          <t>-132.63</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8607,43 +8687,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>7453881.860946746</t>
+          <t>6843513.258</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>44888583.0</t>
+          <t>34949021.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>17133672.6</v>
+        <v>9100308.4</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>10065617.0</t>
+          <t>5742805.4</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>3634806.6</v>
+        <v>2789036.3</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>7068055</t>
+          <t>3357503</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>1120641.91613044</t>
+          <t>441852.6129785951</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>4853983.083465392</t>
+          <t>2463310.163880822</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>44888583.0</t>
+          <t>34949021.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8663,7 +8743,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>-17.28</t>
+          <t>-24.79</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8708,7 +8788,7 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -8718,12 +8798,12 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -8748,12 +8828,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8773,22 +8853,22 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8808,14 +8888,19 @@
       </c>
       <c r="CX17" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="CY17" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8825,12 +8910,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>789.819</t>
+          <t>50.507</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8840,7 +8925,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8850,17 +8935,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-5.44</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>58.46</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8870,37 +8955,37 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2025-06-27 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2025-07-07 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2024-11-07 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2024-11-13 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -8910,12 +8995,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -8925,22 +9010,22 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-26.52</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024/11/05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -8950,7 +9035,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8965,12 +9050,12 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2024/11/19</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>69.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -9000,17 +9085,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>52.90</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>7.21</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -9026,42 +9111,42 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>90</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>7.55</v>
+        <v>-0.61</v>
       </c>
       <c r="AV18" t="n">
-        <v>-0.22</v>
+        <v>-1.42</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>41.47000000000001</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>41.56</v>
+        <v>41.39</v>
       </c>
       <c r="BA18" t="n">
         <v>42.22</v>
@@ -9073,14 +9158,14 @@
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>64.79</t>
+          <t>-14.25</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>-0.11</v>
+        <v>-0.42</v>
       </c>
       <c r="BE18" t="n">
-        <v>-0.32</v>
+        <v>-0.37</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9089,7 +9174,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-132.66</t>
+          <t>-137.92</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9099,43 +9184,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>7453881.860946746</t>
+          <t>6843513.258</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>34949021.0</t>
+          <t>2057561.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>9100308.4</v>
+        <v>2419050.6</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>5742805.4</t>
+          <t>2423375.9</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>2789036.3</v>
+        <v>2195699.04</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>3357503</t>
+          <t>-4325</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>441852.6129786303</t>
+          <t>74314.87645091742</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>2463310.16388083</t>
+          <t>25040.84433570458</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>34949021.0</t>
+          <t>2057561.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9155,7 +9240,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>-24.79</t>
+          <t>-31.62</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9200,22 +9285,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9240,12 +9325,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9265,22 +9350,22 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9300,7 +9385,12 @@
       </c>
       <c r="CX18" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="CY18" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9317,12 +9407,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>50.507</t>
+          <t>52.072</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9332,7 +9422,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9342,17 +9432,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9362,37 +9452,37 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2025-06-27 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2025-07-07 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2024-11-07 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2024-11-13 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -9402,12 +9492,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -9417,22 +9507,22 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-33.20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024/11/05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -9442,7 +9532,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9457,12 +9547,12 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2024/11/19</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>69.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -9492,17 +9582,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9518,7 +9608,7 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>90</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -9532,47 +9622,47 @@
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>-0.61</v>
+        <v>-0.98</v>
       </c>
       <c r="AV19" t="n">
-        <v>-1.42</v>
+        <v>-1.06</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>41.39</v>
+        <v>41.44</v>
       </c>
       <c r="BA19" t="n">
-        <v>42.22</v>
+        <v>42.27</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.29</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-14.25</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>-0.42</v>
+        <v>-0.39</v>
       </c>
       <c r="BE19" t="n">
-        <v>-0.37</v>
+        <v>-0.35</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9581,7 +9671,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-137.95</t>
+          <t>-136.57</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9591,43 +9681,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>7453881.860946746</t>
+          <t>6843513.258</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>2057561.0</t>
+          <t>2118083.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>2419050.6</v>
+        <v>2732836.8</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>2423375.9</t>
+          <t>2355995.8</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>2195699.04</v>
+        <v>2171316.48</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-4325</t>
+          <t>376841</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>74314.87645095764</t>
+          <t>83273.79138095611</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>25040.84433571342</t>
+          <t>64989.64340211917</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>2057561.0</t>
+          <t>2118083.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9647,7 +9737,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>-31.62</t>
+          <t>-31.53</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9697,7 +9787,7 @@
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
@@ -9707,7 +9797,7 @@
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9732,12 +9822,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9757,22 +9847,22 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9792,7 +9882,12 @@
       </c>
       <c r="CX19" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="CY19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9809,12 +9904,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>52.072</t>
+          <t>40.565</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9824,7 +9919,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9834,17 +9929,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>22.82</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9854,37 +9949,37 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2025-06-27 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-07-07 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2024-11-07 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2024-11-13 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -9894,12 +9989,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -9909,22 +10004,22 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-33.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024/11/05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -9934,7 +10029,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9949,12 +10044,12 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2024/11/19</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>69.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -9984,17 +10079,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -10010,7 +10105,7 @@
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>90</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -10020,51 +10115,51 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>-0.98</v>
+        <v>-1.21</v>
       </c>
       <c r="AV20" t="n">
-        <v>-1.06</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>41.44</v>
+        <v>41.49</v>
       </c>
       <c r="BA20" t="n">
-        <v>42.27</v>
+        <v>42.33</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>43.29</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-5.01</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>-0.39</v>
+        <v>-0.36</v>
       </c>
       <c r="BE20" t="n">
-        <v>-0.35</v>
+        <v>-0.34</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
@@ -10073,7 +10168,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-136.60</t>
+          <t>-135.53</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -10083,43 +10178,43 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>7453881.860946746</t>
+          <t>6843513.258</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>2118083.0</t>
+          <t>1655115.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>2732836.8</v>
+        <v>2882296.2</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>2355995.8</t>
+          <t>2346796.6</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>2171316.48</v>
+        <v>2197559.12</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>376841</t>
+          <t>535499</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>83273.79138100205</t>
+          <t>86598.18192256283</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>64989.64340212941</t>
+          <t>113253.7976612072</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>2118083.0</t>
+          <t>1655115.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10139,7 +10234,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>-31.53</t>
+          <t>-31.37</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10184,7 +10279,7 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
@@ -10199,7 +10294,7 @@
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10224,12 +10319,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10249,22 +10344,22 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10284,14 +10379,19 @@
       </c>
       <c r="CX20" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="CY20" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -10301,12 +10401,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>40.565</t>
+          <t>115.01</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10316,149 +10416,149 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>40.9</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>20.99</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2025/07/31</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>58.8</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>2026/01/22</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
           <t>40.7</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>3.78</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2.34</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>22.82</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2025-06-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2024-11-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2024-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>61.2</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>60.7</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>70.8</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>69.7</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>-32.95</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>-12.20</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2024/11/05</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>70.7</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>2025/07/31</t>
-        </is>
-      </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>58.8</t>
-        </is>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>2024/11/19</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>69.4</t>
-        </is>
-      </c>
-      <c r="AG21" t="inlineStr">
-        <is>
-          <t>2026/01/22</t>
-        </is>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>40.7</t>
-        </is>
-      </c>
       <c r="AI21" t="inlineStr">
         <is>
           <t>2025/12/11</t>
@@ -10476,17 +10576,17 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>7.70</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10502,7 +10602,7 @@
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>90</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -10512,48 +10612,48 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>14.04</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>-1.21</v>
+        <v>-1.35</v>
       </c>
       <c r="AV21" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.16</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.45999999999999</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>41.49</v>
+        <v>41.53</v>
       </c>
       <c r="BA21" t="n">
-        <v>42.33</v>
+        <v>42.38</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-5.01</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>-0.36</v>
+        <v>-0.32</v>
       </c>
       <c r="BE21" t="n">
         <v>-0.34</v>
@@ -10565,7 +10665,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-135.57</t>
+          <t>-135.08</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10575,43 +10675,43 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>7453881.860946746</t>
+          <t>6843513.258</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>1655115.0</t>
+          <t>4721762.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>2882296.2</v>
+        <v>2997561.4</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>2346796.6</t>
+          <t>2477506.7</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>2197559.12</v>
+        <v>2270637.82</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>535499</t>
+          <t>520054</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>86598.18192261527</t>
+          <t>81751.70633371841</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>113253.7976612188</t>
+          <t>227761.5252577183</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>1655115.0</t>
+          <t>4721762.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10631,7 +10731,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>-31.37</t>
+          <t>-31.03</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10676,22 +10776,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10716,12 +10816,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10741,22 +10841,22 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10776,29 +10876,34 @@
       </c>
       <c r="CX21" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="CY21" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>6504</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>115.01</t>
+          <t>196.33</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10808,7 +10913,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10818,17 +10923,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>19.16</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10838,37 +10943,37 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2025-06-27 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-07-07 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2024-11-07 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2024-11-13 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -10878,12 +10983,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -10893,22 +10998,22 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-32.62</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024/11/05</t>
+          <t>2025/09/18</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -10918,67 +11023,67 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2025/07/31</t>
+          <t>2025/12/24</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2024/11/19</t>
+          <t>2025/10/08</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>69.4</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>2026/01/22</t>
+          <t>2025/12/12</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>2025/12/11</t>
+          <t>2025/11/05</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>64.6</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2026-01-27 00:00:00</t>
+          <t>2025-05-28 00:00:00</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>7.70</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10989,121 +11094,121 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>14.04</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>-1.35</v>
+        <v>-0.41</v>
       </c>
       <c r="AV22" t="n">
-        <v>-0.16</v>
+        <v>-1.77</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>41.45999999999999</t>
+          <t>63.36</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>41.53</v>
+        <v>64.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>42.38</v>
+        <v>65.28</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>66.79</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>-11.64</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>-0.32</v>
+        <v>-0.75</v>
       </c>
       <c r="BE22" t="n">
-        <v>-0.34</v>
+        <v>-0.67</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-135.12</t>
+          <t>-130.21</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026/01/27</t>
+          <t>2025/11/12</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>7453881.860946746</t>
+          <t>22727652.70742358</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>4721762.0</t>
+          <t>12405920.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>2997561.4</v>
+        <v>7565674.4</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>2477506.7</t>
+          <t>6349216.5</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>2270637.82</v>
+        <v>6294708.94</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>520054</t>
+          <t>1216457</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>81751.70633377827</t>
+          <t>57194.83318975937</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>227761.5252577313</t>
+          <t>777936.1308340589</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>4721762.0</t>
+          <t>12405920.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -11113,32 +11218,32 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>59.3</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>2025/05/26</t>
+          <t>2025/12/19</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>-31.03</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>南六</t>
+          <t>寶齡富錦</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
         <is>
-          <t>南六</t>
+          <t>寶齡富錦</t>
         </is>
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
@@ -11148,27 +11253,27 @@
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
         <is>
-          <t>-3.675038602250755</t>
+          <t>-22.55378299170716</t>
         </is>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>-14.32073522315297</t>
+          <t>14.88387829883942</t>
         </is>
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>-1.501881912730951</t>
+          <t>1.662704561635163</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
@@ -11178,87 +11283,87 @@
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
         <is>
-          <t>22.20</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31.28</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
         <is>
-          <t>12.86%</t>
+          <t>56.45%</t>
         </is>
       </c>
       <c r="CK22" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>18.71%</t>
         </is>
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>57.44</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>5444</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
         <is>
-          <t>PP不織布30.93%、生技產品28.88%、水針布27.86%、水針後處理12.33% (2024年)</t>
+          <t>藥品38.92%、權利金收入20.27%、食品17.41%、化工8.69%、原料藥(API)8.12%、檢驗試劑5.07%、里程金1.10%、醫美醫材0.43% (2024年)</t>
         </is>
       </c>
       <c r="CO22" t="inlineStr">
         <is>
-          <t>南六-其他-上市</t>
+          <t>寶齡富錦-生技醫療業-上市</t>
         </is>
       </c>
       <c r="CP22" t="inlineStr">
         <is>
-          <t>其他右下上市</t>
+          <t>生技醫療業右下上市</t>
         </is>
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>64.1</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>62.8</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
         <is>
-          <t>44.62</t>
+          <t>22.18</t>
         </is>
       </c>
       <c r="CV22" t="inlineStr">
         <is>
-          <t>** 石化及塑橡膠 - 清潔用品、化妝品** 紡織 - 成衣及其它家居紡織類品** 醫療器材 - 衛生用品、醫療耗材</t>
+          <t>** 石化及塑橡膠 - 化妝品** 製藥 - 中、西藥製劑、藥品代理銷售及通路** 食品生技 - 加工製成品、保健食品代理銷售及通路** 醫療器材 - 醫療耗材、生物檢測</t>
         </is>
       </c>
       <c r="CW22" t="inlineStr">
@@ -11268,29 +11373,34 @@
       </c>
       <c r="CX22" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CY22" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>6504</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>37.287</t>
+          <t>170.283</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11300,7 +11410,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>63.7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11310,17 +11420,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>9.80</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11330,37 +11440,37 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2025-06-27 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025-07-07 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2024-11-07 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2024-11-13 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -11370,12 +11480,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -11385,22 +11495,22 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-32.04</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024/11/05</t>
+          <t>2025/09/18</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -11410,67 +11520,67 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2025/07/31</t>
+          <t>2025/12/24</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2024/11/19</t>
+          <t>2025/10/08</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>69.4</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>2026/01/22</t>
+          <t>2025/12/12</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>2025/12/11</t>
+          <t>2025/11/05</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>64.6</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2026-01-27 00:00:00</t>
+          <t>2025-05-28 00:00:00</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11481,121 +11591,121 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>31.57</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>-0.63</v>
+        <v>0.54</v>
       </c>
       <c r="AV23" t="n">
-        <v>-0.16</v>
+        <v>-2.12</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>41.51</t>
+          <t>63.36</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>41.58</v>
+        <v>64.73</v>
       </c>
       <c r="BA23" t="n">
-        <v>42.41</v>
+        <v>65.37</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>43.47</t>
+          <t>66.91</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>14.85</t>
+          <t>-13.92</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>-0.29</v>
+        <v>-0.74</v>
       </c>
       <c r="BE23" t="n">
-        <v>-0.34</v>
+        <v>-0.65</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-135.52</t>
+          <t>-129.33</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026/01/27</t>
+          <t>2025/11/12</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>7453881.860946746</t>
+          <t>22727652.70742358</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>1542732.0</t>
+          <t>10912503.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>2385302.4</v>
+        <v>6082012.6</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>2294484.4</t>
+          <t>5539199.3</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>2236735.98</v>
+        <v>6314109.14</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>90818</t>
+          <t>542813</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>55204.46652942317</t>
+          <t>-73849.03910920418</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>54640.33163640229</t>
+          <t>361830.4726516372</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>1542732.0</t>
+          <t>10912503.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11605,32 +11715,32 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>59.3</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>2025/05/26</t>
+          <t>2025/12/19</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>-30.44</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>南六</t>
+          <t>寶齡富錦</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
         <is>
-          <t>南六</t>
+          <t>寶齡富錦</t>
         </is>
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>生技醫療業</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
@@ -11640,27 +11750,27 @@
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
         <is>
-          <t>-3.675038602250755</t>
+          <t>-22.55378299170716</t>
         </is>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>-14.32073522315297</t>
+          <t>14.88387829883942</t>
         </is>
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>-1.501881912730951</t>
+          <t>1.662704561635163</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
@@ -11670,87 +11780,87 @@
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
         <is>
-          <t>22.20</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31.28</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
         <is>
-          <t>12.86%</t>
+          <t>56.45%</t>
         </is>
       </c>
       <c r="CK23" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>18.71%</t>
         </is>
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>57.44</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>5444</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
         <is>
-          <t>PP不織布30.93%、生技產品28.88%、水針布27.86%、水針後處理12.33% (2024年)</t>
+          <t>藥品38.92%、權利金收入20.27%、食品17.41%、化工8.69%、原料藥(API)8.12%、檢驗試劑5.07%、里程金1.10%、醫美醫材0.43% (2024年)</t>
         </is>
       </c>
       <c r="CO23" t="inlineStr">
         <is>
-          <t>南六-其他-上市</t>
+          <t>寶齡富錦-生技醫療業-上市</t>
         </is>
       </c>
       <c r="CP23" t="inlineStr">
         <is>
-          <t>其他右下上市</t>
+          <t>生技醫療業右下上市</t>
         </is>
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>63.6</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>63.7</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
         <is>
-          <t>44.62</t>
+          <t>22.18</t>
         </is>
       </c>
       <c r="CV23" t="inlineStr">
         <is>
-          <t>** 石化及塑橡膠 - 清潔用品、化妝品** 紡織 - 成衣及其它家居紡織類品** 醫療器材 - 衛生用品、醫療耗材</t>
+          <t>** 石化及塑橡膠 - 化妝品** 製藥 - 中、西藥製劑、藥品代理銷售及通路** 食品生技 - 加工製成品、保健食品代理銷售及通路** 醫療器材 - 醫療耗材、生物檢測</t>
         </is>
       </c>
       <c r="CW23" t="inlineStr">
@@ -11760,29 +11870,34 @@
       </c>
       <c r="CX23" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CY23" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1760</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>196.33</t>
+          <t>52.658</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11792,7 +11907,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -11802,17 +11917,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>-1.07</t>
-        </is>
-      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>19.16</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -11827,32 +11942,32 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-08-04 00:00:00</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-08-20 00:00:00</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-25 00:00:00</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-28 00:00:00</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>33.05</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -11862,12 +11977,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32.75</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -11877,22 +11992,22 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025/09/18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -11902,52 +12017,52 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2025/12/24</t>
+          <t>2025/08/28</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>2025/10/08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>2025/12/12</t>
+          <t>2025/12/10</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>2025/11/05</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>64.6</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>2025-05-28 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
@@ -11957,12 +12072,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>5.18</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -11973,121 +12088,121 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>-0.41</v>
+        <v>-0.32</v>
       </c>
       <c r="AV24" t="n">
-        <v>-1.77</v>
+        <v>0.04</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>63.36</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>64.5</v>
+        <v>31.59</v>
       </c>
       <c r="BA24" t="n">
-        <v>65.28</v>
+        <v>31.71</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>66.79</t>
+          <t>31.87</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>-11.64</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="BD24" t="n">
-        <v>-0.75</v>
+        <v>-0.04</v>
       </c>
       <c r="BE24" t="n">
-        <v>-0.67</v>
+        <v>-0.04</v>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-130.09</t>
+          <t>-118.35</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/19</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>39991174.25</t>
+          <t>5770029.975982533</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>12405920.0</t>
+          <t>1660091.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>7565674.4</v>
+        <v>3220987.4</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>6349216.5</t>
+          <t>3083421.0</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>6294708.94</v>
+        <v>3297756.66</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>1216457</t>
+          <t>137566</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>57194.83320573541</t>
+          <t>-16709.90572457966</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>777936.1308374852</t>
+          <t>-87417.93593258597</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>12405920.0</t>
+          <t>1660091.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -12097,32 +12212,32 @@
       </c>
       <c r="BS24" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>32.7</t>
         </is>
       </c>
       <c r="BT24" t="inlineStr">
         <is>
-          <t>2025/12/19</t>
+          <t>2025/05/19</t>
         </is>
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
         <is>
-          <t>寶齡富錦</t>
+          <t>臺鹽</t>
         </is>
       </c>
       <c r="BW24" t="inlineStr">
         <is>
-          <t>寶齡富錦</t>
+          <t>臺鹽</t>
         </is>
       </c>
       <c r="BX24" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>食品工業</t>
         </is>
       </c>
       <c r="BY24" t="inlineStr">
@@ -12132,27 +12247,27 @@
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
         <is>
-          <t>-22.55378299170716</t>
+          <t>11.30964198266164</t>
         </is>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>14.88387829883942</t>
+          <t>7.950770160072485</t>
         </is>
       </c>
       <c r="CC24" t="inlineStr">
         <is>
-          <t>1.662704561635163</t>
+          <t>2.099499961706554</t>
         </is>
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
@@ -12162,87 +12277,87 @@
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="CI24" t="inlineStr">
         <is>
-          <t>31.08</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="CJ24" t="inlineStr">
         <is>
-          <t>56.45%</t>
+          <t>39.76%</t>
         </is>
       </c>
       <c r="CK24" t="inlineStr">
         <is>
-          <t>18.71%</t>
+          <t>11.78%</t>
         </is>
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>56.92</t>
+          <t>25.62</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>5410</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
         <is>
-          <t>藥品38.92%、權利金收入20.27%、食品17.41%、化工8.69%、原料藥(API)8.12%、檢驗試劑5.07%、里程金1.10%、醫美醫材0.43% (2024年)</t>
+          <t>鹽46.50%、包裝飲用水34.02%、清潔用品5.33%、保健食品5.08%、美容保養品4.12%、工程及勞務2.55%、其他2.39% (2024年)</t>
         </is>
       </c>
       <c r="CO24" t="inlineStr">
         <is>
-          <t>寶齡富錦-生技醫療業-上市</t>
+          <t>臺鹽-食品工業-上市</t>
         </is>
       </c>
       <c r="CP24" t="inlineStr">
         <is>
-          <t>生技醫療業右下上市</t>
+          <t>食品工業右下上市</t>
         </is>
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
-          <t>64.1</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="CR24" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
-          <t>62.8</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="CT24" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>33.23</t>
         </is>
       </c>
       <c r="CV24" t="inlineStr">
         <is>
-          <t>** 石化及塑橡膠 - 化妝品** 製藥 - 中、西藥製劑、藥品代理銷售及通路** 食品生技 - 加工製成品、保健食品代理銷售及通路** 醫療器材 - 醫療耗材、生物檢測</t>
+          <t>** 食品 - 原物料、營養食品** 石化及塑橡膠 - 化妝品</t>
         </is>
       </c>
       <c r="CW24" t="inlineStr">
@@ -12252,29 +12367,34 @@
       </c>
       <c r="CX24" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="CY24" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1760</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>170.283</t>
+          <t>81.467</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12284,7 +12404,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>63.7</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -12294,17 +12414,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>9.80</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12319,32 +12439,32 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-08-04 00:00:00</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-08-20 00:00:00</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-25 00:00:00</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-28 00:00:00</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>33.05</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -12354,12 +12474,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32.75</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -12369,22 +12489,22 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025/09/18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -12394,52 +12514,52 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2025/12/24</t>
+          <t>2025/08/28</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>2025/10/08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>2025/12/12</t>
+          <t>2025/12/10</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>2025/11/05</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>64.6</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>2025-05-28 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
@@ -12449,12 +12569,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -12465,121 +12585,121 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>31.57</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>0.54</v>
+        <v>-0.44</v>
       </c>
       <c r="AV25" t="n">
-        <v>-2.12</v>
+        <v>0.14</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>63.36</t>
+          <t>31.64</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>64.73</v>
+        <v>31.6</v>
       </c>
       <c r="BA25" t="n">
-        <v>65.37</v>
+        <v>31.72</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>66.91</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-13.92</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="BD25" t="n">
-        <v>-0.74</v>
+        <v>-0.03</v>
       </c>
       <c r="BE25" t="n">
-        <v>-0.65</v>
+        <v>-0.04</v>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-129.21</t>
+          <t>-118.73</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/19</t>
         </is>
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>39991174.25</t>
+          <t>5770029.975982533</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>10912503.0</t>
+          <t>2568418.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>6082012.6</v>
+        <v>3289054.2</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>5539199.3</t>
+          <t>3137217.9</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>6314109.14</v>
+        <v>3324051.1</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>542813</t>
+          <t>151836</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>-73849.03909094637</t>
+          <t>-3853.900232214874</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>361830.4726555534</t>
+          <t>32790.85744641861</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>10912503.0</t>
+          <t>2568418.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -12589,32 +12709,32 @@
       </c>
       <c r="BS25" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>32.7</t>
         </is>
       </c>
       <c r="BT25" t="inlineStr">
         <is>
-          <t>2025/12/19</t>
+          <t>2025/05/19</t>
         </is>
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
         <is>
-          <t>寶齡富錦</t>
+          <t>臺鹽</t>
         </is>
       </c>
       <c r="BW25" t="inlineStr">
         <is>
-          <t>寶齡富錦</t>
+          <t>臺鹽</t>
         </is>
       </c>
       <c r="BX25" t="inlineStr">
         <is>
-          <t>生技醫療業</t>
+          <t>食品工業</t>
         </is>
       </c>
       <c r="BY25" t="inlineStr">
@@ -12624,27 +12744,27 @@
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
         <is>
-          <t>-22.55378299170716</t>
+          <t>11.30964198266164</t>
         </is>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>14.88387829883942</t>
+          <t>7.950770160072485</t>
         </is>
       </c>
       <c r="CC25" t="inlineStr">
         <is>
-          <t>1.662704561635163</t>
+          <t>2.099499961706554</t>
         </is>
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
@@ -12654,87 +12774,87 @@
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="CI25" t="inlineStr">
         <is>
-          <t>31.08</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="CJ25" t="inlineStr">
         <is>
-          <t>56.45%</t>
+          <t>39.76%</t>
         </is>
       </c>
       <c r="CK25" t="inlineStr">
         <is>
-          <t>18.71%</t>
+          <t>11.78%</t>
         </is>
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>56.92</t>
+          <t>25.62</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>5410</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
         <is>
-          <t>藥品38.92%、權利金收入20.27%、食品17.41%、化工8.69%、原料藥(API)8.12%、檢驗試劑5.07%、里程金1.10%、醫美醫材0.43% (2024年)</t>
+          <t>鹽46.50%、包裝飲用水34.02%、清潔用品5.33%、保健食品5.08%、美容保養品4.12%、工程及勞務2.55%、其他2.39% (2024年)</t>
         </is>
       </c>
       <c r="CO25" t="inlineStr">
         <is>
-          <t>寶齡富錦-生技醫療業-上市</t>
+          <t>臺鹽-食品工業-上市</t>
         </is>
       </c>
       <c r="CP25" t="inlineStr">
         <is>
-          <t>生技醫療業右下上市</t>
+          <t>食品工業右下上市</t>
         </is>
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CR25" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
-          <t>63.6</t>
+          <t>31.45</t>
         </is>
       </c>
       <c r="CT25" t="inlineStr">
         <is>
-          <t>63.7</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>33.23</t>
         </is>
       </c>
       <c r="CV25" t="inlineStr">
         <is>
-          <t>** 石化及塑橡膠 - 化妝品** 製藥 - 中、西藥製劑、藥品代理銷售及通路** 食品生技 - 加工製成品、保健食品代理銷售及通路** 醫療器材 - 醫療耗材、生物檢測</t>
+          <t>** 食品 - 原物料、營養食品** 石化及塑橡膠 - 化妝品</t>
         </is>
       </c>
       <c r="CW25" t="inlineStr">
@@ -12744,991 +12864,12 @@
       </c>
       <c r="CX25" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>【d1】</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1737</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>52.658</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>31.5</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>4.46</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>2025-08-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>2025-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>2025-07-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>2025-07-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>33.05</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>32.25</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>32.9</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>32.75</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>-2.33</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2025/02/21</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>32.7</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>2025/08/28</t>
-        </is>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>32.2</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>2025/04/08</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>30.65</t>
-        </is>
-      </c>
-      <c r="AG26" t="inlineStr">
-        <is>
-          <t>2025/12/10</t>
-        </is>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>31.6</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>2025/12/08</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>31.6</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>2025-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL26" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>5.18</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>-0.32</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP26" t="inlineStr"/>
-      <c r="AQ26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="AS26" t="inlineStr">
-        <is>
-          <t>14.29</t>
-        </is>
-      </c>
-      <c r="AT26" t="inlineStr">
-        <is>
-          <t>33.33</t>
-        </is>
-      </c>
-      <c r="AU26" t="n">
-        <v>-0.32</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>-0.39</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>-0.49</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>31.6</t>
-        </is>
-      </c>
-      <c r="AZ26" t="n">
-        <v>31.59</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>31.71</v>
-      </c>
-      <c r="BB26" t="inlineStr">
-        <is>
-          <t>31.87</t>
-        </is>
-      </c>
-      <c r="BC26" t="inlineStr">
-        <is>
-          <t>8.23</t>
-        </is>
-      </c>
-      <c r="BD26" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="BF26" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="BG26" t="inlineStr">
-        <is>
-          <t>-113.78</t>
-        </is>
-      </c>
-      <c r="BH26" t="inlineStr">
-        <is>
-          <t>2025/12/19</t>
-        </is>
-      </c>
-      <c r="BI26" t="inlineStr">
-        <is>
-          <t>11302230.99382716</t>
-        </is>
-      </c>
-      <c r="BJ26" t="inlineStr">
-        <is>
-          <t>1660091.0</t>
-        </is>
-      </c>
-      <c r="BK26" t="n">
-        <v>3220987.4</v>
-      </c>
-      <c r="BL26" t="inlineStr">
-        <is>
-          <t>3083421.0</t>
-        </is>
-      </c>
-      <c r="BM26" t="n">
-        <v>3297756.66</v>
-      </c>
-      <c r="BN26" t="inlineStr">
-        <is>
-          <t>137566</t>
-        </is>
-      </c>
-      <c r="BO26" t="inlineStr">
-        <is>
-          <t>-16709.90572409765</t>
-        </is>
-      </c>
-      <c r="BP26" t="inlineStr">
-        <is>
-          <t>-87417.93593248213</t>
-        </is>
-      </c>
-      <c r="BQ26" t="inlineStr">
-        <is>
-          <t>1660091.0</t>
-        </is>
-      </c>
-      <c r="BR26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS26" t="inlineStr">
-        <is>
-          <t>32.7</t>
-        </is>
-      </c>
-      <c r="BT26" t="inlineStr">
-        <is>
-          <t>2025/05/19</t>
-        </is>
-      </c>
-      <c r="BU26" t="inlineStr">
-        <is>
-          <t>-3.67</t>
-        </is>
-      </c>
-      <c r="BV26" t="inlineStr">
-        <is>
-          <t>臺鹽</t>
-        </is>
-      </c>
-      <c r="BW26" t="inlineStr">
-        <is>
-          <t>臺鹽</t>
-        </is>
-      </c>
-      <c r="BX26" t="inlineStr">
-        <is>
-          <t>食品工業</t>
-        </is>
-      </c>
-      <c r="BY26" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ26" t="inlineStr">
-        <is>
-          <t>0.28</t>
-        </is>
-      </c>
-      <c r="CA26" t="inlineStr">
-        <is>
-          <t>11.30964198266164</t>
-        </is>
-      </c>
-      <c r="CB26" t="inlineStr">
-        <is>
-          <t>7.950770160072485</t>
-        </is>
-      </c>
-      <c r="CC26" t="inlineStr">
-        <is>
-          <t>2.099499961706554</t>
-        </is>
-      </c>
-      <c r="CD26" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE26" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF26" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
-      </c>
-      <c r="CG26" t="inlineStr">
-        <is>
-          <t>4.13</t>
-        </is>
-      </c>
-      <c r="CH26" t="inlineStr">
-        <is>
-          <t>4.07</t>
-        </is>
-      </c>
-      <c r="CI26" t="inlineStr">
-        <is>
-          <t>18.86</t>
-        </is>
-      </c>
-      <c r="CJ26" t="inlineStr">
-        <is>
-          <t>39.76%</t>
-        </is>
-      </c>
-      <c r="CK26" t="inlineStr">
-        <is>
-          <t>11.78%</t>
-        </is>
-      </c>
-      <c r="CL26" t="inlineStr">
-        <is>
-          <t>25.51</t>
-        </is>
-      </c>
-      <c r="CM26" t="inlineStr">
-        <is>
-          <t>6300</t>
-        </is>
-      </c>
-      <c r="CN26" t="inlineStr">
-        <is>
-          <t>鹽46.50%、包裝飲用水34.02%、清潔用品5.33%、保健食品5.08%、美容保養品4.12%、工程及勞務2.55%、其他2.39% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO26" t="inlineStr">
-        <is>
-          <t>臺鹽-食品工業-上市</t>
-        </is>
-      </c>
-      <c r="CP26" t="inlineStr">
-        <is>
-          <t>食品工業右下上市</t>
-        </is>
-      </c>
-      <c r="CQ26" t="inlineStr">
-        <is>
-          <t>31.5</t>
-        </is>
-      </c>
-      <c r="CR26" t="inlineStr">
-        <is>
-          <t>31.6</t>
-        </is>
-      </c>
-      <c r="CS26" t="inlineStr">
-        <is>
-          <t>31.5</t>
-        </is>
-      </c>
-      <c r="CT26" t="inlineStr">
-        <is>
-          <t>31.5</t>
-        </is>
-      </c>
-      <c r="CU26" t="inlineStr">
-        <is>
-          <t>33.23</t>
-        </is>
-      </c>
-      <c r="CV26" t="inlineStr">
-        <is>
-          <t>** 食品 - 原物料、營養食品** 石化及塑橡膠 - 化妝品</t>
-        </is>
-      </c>
-      <c r="CW26" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="CX26" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>【d1】</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1737</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>-0.32</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>81.467</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>31.5</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>4.84</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>2025-08-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>2025-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>2025-07-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>2025-07-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>33.05</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>32.25</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>32.9</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>32.75</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>-2.33</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2025/02/21</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>32.7</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>2025/08/28</t>
-        </is>
-      </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>32.2</t>
-        </is>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>2025/04/08</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>30.65</t>
-        </is>
-      </c>
-      <c r="AG27" t="inlineStr">
-        <is>
-          <t>2025/12/10</t>
-        </is>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>31.6</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>2025/12/08</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>31.6</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>2025-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL27" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>8.01</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>-0.16</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP27" t="inlineStr"/>
-      <c r="AQ27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="AS27" t="inlineStr">
-        <is>
-          <t>14.29</t>
-        </is>
-      </c>
-      <c r="AT27" t="inlineStr">
-        <is>
-          <t>42.86</t>
-        </is>
-      </c>
-      <c r="AU27" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>-0.4</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>-0.49</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t>31.64</t>
-        </is>
-      </c>
-      <c r="AZ27" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>31.72</v>
-      </c>
-      <c r="BB27" t="inlineStr">
-        <is>
-          <t>31.88</t>
-        </is>
-      </c>
-      <c r="BC27" t="inlineStr">
-        <is>
-          <t>25.55</t>
-        </is>
-      </c>
-      <c r="BD27" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="BF27" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="BG27" t="inlineStr">
-        <is>
-          <t>-114.07</t>
-        </is>
-      </c>
-      <c r="BH27" t="inlineStr">
-        <is>
-          <t>2025/12/19</t>
-        </is>
-      </c>
-      <c r="BI27" t="inlineStr">
-        <is>
-          <t>11302230.99382716</t>
-        </is>
-      </c>
-      <c r="BJ27" t="inlineStr">
-        <is>
-          <t>2568418.0</t>
-        </is>
-      </c>
-      <c r="BK27" t="n">
-        <v>3289054.2</v>
-      </c>
-      <c r="BL27" t="inlineStr">
-        <is>
-          <t>3137217.9</t>
-        </is>
-      </c>
-      <c r="BM27" t="n">
-        <v>3324051.1</v>
-      </c>
-      <c r="BN27" t="inlineStr">
-        <is>
-          <t>151836</t>
-        </is>
-      </c>
-      <c r="BO27" t="inlineStr">
-        <is>
-          <t>-3853.900231664111</t>
-        </is>
-      </c>
-      <c r="BP27" t="inlineStr">
-        <is>
-          <t>32790.85744653689</t>
-        </is>
-      </c>
-      <c r="BQ27" t="inlineStr">
-        <is>
-          <t>2568418.0</t>
-        </is>
-      </c>
-      <c r="BR27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS27" t="inlineStr">
-        <is>
-          <t>32.7</t>
-        </is>
-      </c>
-      <c r="BT27" t="inlineStr">
-        <is>
-          <t>2025/05/19</t>
-        </is>
-      </c>
-      <c r="BU27" t="inlineStr">
-        <is>
-          <t>-3.67</t>
-        </is>
-      </c>
-      <c r="BV27" t="inlineStr">
-        <is>
-          <t>臺鹽</t>
-        </is>
-      </c>
-      <c r="BW27" t="inlineStr">
-        <is>
-          <t>臺鹽</t>
-        </is>
-      </c>
-      <c r="BX27" t="inlineStr">
-        <is>
-          <t>食品工業</t>
-        </is>
-      </c>
-      <c r="BY27" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ27" t="inlineStr">
-        <is>
-          <t>0.28</t>
-        </is>
-      </c>
-      <c r="CA27" t="inlineStr">
-        <is>
-          <t>11.30964198266164</t>
-        </is>
-      </c>
-      <c r="CB27" t="inlineStr">
-        <is>
-          <t>7.950770160072485</t>
-        </is>
-      </c>
-      <c r="CC27" t="inlineStr">
-        <is>
-          <t>2.099499961706554</t>
-        </is>
-      </c>
-      <c r="CD27" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE27" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF27" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
-      </c>
-      <c r="CG27" t="inlineStr">
-        <is>
-          <t>4.13</t>
-        </is>
-      </c>
-      <c r="CH27" t="inlineStr">
-        <is>
-          <t>4.07</t>
-        </is>
-      </c>
-      <c r="CI27" t="inlineStr">
-        <is>
-          <t>18.86</t>
-        </is>
-      </c>
-      <c r="CJ27" t="inlineStr">
-        <is>
-          <t>39.76%</t>
-        </is>
-      </c>
-      <c r="CK27" t="inlineStr">
-        <is>
-          <t>11.78%</t>
-        </is>
-      </c>
-      <c r="CL27" t="inlineStr">
-        <is>
-          <t>25.51</t>
-        </is>
-      </c>
-      <c r="CM27" t="inlineStr">
-        <is>
-          <t>6300</t>
-        </is>
-      </c>
-      <c r="CN27" t="inlineStr">
-        <is>
-          <t>鹽46.50%、包裝飲用水34.02%、清潔用品5.33%、保健食品5.08%、美容保養品4.12%、工程及勞務2.55%、其他2.39% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO27" t="inlineStr">
-        <is>
-          <t>臺鹽-食品工業-上市</t>
-        </is>
-      </c>
-      <c r="CP27" t="inlineStr">
-        <is>
-          <t>食品工業右下上市</t>
-        </is>
-      </c>
-      <c r="CQ27" t="inlineStr">
-        <is>
-          <t>31.6</t>
-        </is>
-      </c>
-      <c r="CR27" t="inlineStr">
-        <is>
-          <t>31.6</t>
-        </is>
-      </c>
-      <c r="CS27" t="inlineStr">
-        <is>
-          <t>31.45</t>
-        </is>
-      </c>
-      <c r="CT27" t="inlineStr">
-        <is>
-          <t>31.5</t>
-        </is>
-      </c>
-      <c r="CU27" t="inlineStr">
-        <is>
-          <t>33.23</t>
-        </is>
-      </c>
-      <c r="CV27" t="inlineStr">
-        <is>
-          <t>** 食品 - 原物料、營養食品** 石化及塑橡膠 - 化妝品</t>
-        </is>
-      </c>
-      <c r="CW27" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="CX27" t="inlineStr">
-        <is>
-          <t>7.0</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="CY25" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
